--- a/Liquid+ Project/Sélection des startups/processus de sélection des startups GAIA.xlsx
+++ b/Liquid+ Project/Sélection des startups/processus de sélection des startups GAIA.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="1369">
   <si>
     <t>Implantation</t>
   </si>
@@ -2985,6 +2985,9 @@
     <t>Anodine</t>
   </si>
   <si>
+    <t xml:space="preserve"> contact@anodine.fr</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/anodine/people/</t>
   </si>
   <si>
@@ -3003,6 +3006,12 @@
     <t>Krystalix</t>
   </si>
   <si>
+    <t>kader.zaidat@krystalix.com</t>
+  </si>
+  <si>
+    <t>linkedin.com/company/krystalix?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Fabrication de monocristaux haute performance (spin-off Grenoble INP)</t>
   </si>
   <si>
@@ -3012,6 +3021,12 @@
     <t>Saxol</t>
   </si>
   <si>
+    <t>contact @ saxol.eu .</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/saxol/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Biotech – traitement préventif des neuropathies périphériques / effets secondaires de la chimiothérapie (candidat Carba1)</t>
   </si>
   <si>
@@ -3021,6 +3036,12 @@
     <t>React Therapeutics</t>
   </si>
   <si>
+    <t xml:space="preserve">contact@react-therapeutics.com </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/react-therapeutics/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Restaurer l'efficacité des traitements anticancéreux (inhibiteur BCRP / multirésistance)</t>
   </si>
   <si>
@@ -3030,6 +3051,12 @@
     <t>NVEIL</t>
   </si>
   <si>
+    <t>info@nveil.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/nveil/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Plateforme de visualisation et d'analyse de données scientifiques par IA</t>
   </si>
   <si>
@@ -3039,24 +3066,45 @@
     <t>Theyeq</t>
   </si>
   <si>
+    <t>contact@theyeq.com</t>
+  </si>
+  <si>
+    <t>linkedin.com/company/theyeq?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Numérique &amp; Électronique</t>
   </si>
   <si>
     <t>Phonix Health</t>
   </si>
   <si>
+    <t>yves.hemery@linksium.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/joinphoenixhealth/</t>
+  </si>
+  <si>
     <t>Santé – diagnostic et accompagnement de l'addiction numérique</t>
   </si>
   <si>
     <t>Bluetwin</t>
   </si>
   <si>
+    <t>matthieu.minguez@bluetwin.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/bluetwin/</t>
+  </si>
+  <si>
     <t>Énergie &amp; Environnement – éolien</t>
   </si>
   <si>
     <t>Parkinsang</t>
   </si>
   <si>
+    <t xml:space="preserve"> chloe.poyet@linksium.fr</t>
+  </si>
+  <si>
     <t>Santé – biomarqueur sanguin de la maladie de Parkinson</t>
   </si>
   <si>
@@ -3066,6 +3114,12 @@
     <t>Litesense</t>
   </si>
   <si>
+    <t>contact@litesense.io.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/litesense-io/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Numérique &amp; Électronique – capteurs / caméra intelligente</t>
   </si>
   <si>
@@ -3078,12 +3132,21 @@
     <t>Totem</t>
   </si>
   <si>
+    <t>"accueil@neocorner.fr" &lt;accueil@neocorner.fr&gt;</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/totemcult/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Santé – technologie de traitement du cancer</t>
   </si>
   <si>
     <t>Panama</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/panama_3/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Chimie &amp; Matériaux – lithographie</t>
   </si>
   <si>
@@ -3096,36 +3159,66 @@
     <t>Zelinqa</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/zelinqa/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Numérique &amp; Électronique – agents IA</t>
   </si>
   <si>
     <t>Switch2Prod</t>
   </si>
   <si>
+    <t>thibault.clavier@inria.fr.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/thibault-clavier-phd-24aab884/</t>
+  </si>
+  <si>
     <t>Chimie &amp; Matériaux – molécules biosourcées</t>
   </si>
   <si>
     <t>Susinnos</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/susinnos/</t>
+  </si>
+  <si>
     <t>Énergie &amp; Environnement – transition industrielle</t>
   </si>
   <si>
     <t>Injectose</t>
   </si>
   <si>
+    <t xml:space="preserve"> contact@injectose.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/injectose/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Chimie &amp; Matériaux – injection de cellulose</t>
   </si>
   <si>
     <t>Smartpatch Health</t>
   </si>
   <si>
+    <t>contact@smartpatch.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/smartpatch-sportech/</t>
+  </si>
+  <si>
     <t>Santé – biocapteur portable (wearable)</t>
   </si>
   <si>
     <t>Neurosnooper</t>
   </si>
   <si>
+    <t xml:space="preserve">dmd a </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dr. Gaëlle Offranc-Piret</t>
+  </si>
+  <si>
     <t>Santé – implant cérébral</t>
   </si>
   <si>
@@ -3144,43 +3237,76 @@
     <t>Modèle GEC</t>
   </si>
   <si>
+    <t>christine.melay@linksium.fr</t>
+  </si>
+  <si>
+    <t>Dmd le contact</t>
+  </si>
+  <si>
     <t>Santé – stratification du risque (leucémie)</t>
   </si>
   <si>
     <t>Muscle Up</t>
   </si>
   <si>
+    <t>chloe.poyet@linksium.fr</t>
+  </si>
+  <si>
     <t>Santé – mesure de la fonction musculaire</t>
   </si>
   <si>
     <t>Arximed</t>
   </si>
   <si>
+    <t>info@arximed.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/arximed/</t>
+  </si>
+  <si>
     <t>Santé – imagerie médicale</t>
   </si>
   <si>
     <t>Madcap-Nano</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/madcap-nano/</t>
+  </si>
+  <si>
     <t>Chimie &amp; Matériaux – feuillets de graphène</t>
   </si>
   <si>
     <t>Odiasp</t>
   </si>
   <si>
+    <t>odiasp@chu-grenoble.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/c%C3%A9cile-b%C3%A9try-03899442/</t>
+  </si>
+  <si>
     <t>Santé – diagnostic de la sarcopénie par IA</t>
   </si>
   <si>
     <t>Yona Robotics</t>
   </si>
   <si>
+    <t>contact@yona-robotics.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/yona-robotics/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Numérique &amp; Électronique – robotique mobile</t>
   </si>
   <si>
     <t>Histia</t>
   </si>
   <si>
-    <t>linkedin.com/company/histia-app</t>
+    <t>contact@histia.net</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/histia-app/?originalSubdomain=fr</t>
   </si>
   <si>
     <t>Léopold Servais</t>
@@ -3204,7 +3330,10 @@
     <t>Størm Skinwear</t>
   </si>
   <si>
-    <t>linkedin.com/in/lucie-rupt</t>
+    <t>contact@storm-skinwear.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lucie-rupt/</t>
   </si>
   <si>
     <t>Lucie Rupt</t>
@@ -3222,6 +3351,9 @@
     <t>Jerome.moinet@courtierencredits.com | linkedin.com/in/jerome-moinet</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Jérôme Moinet</t>
   </si>
   <si>
@@ -3231,7 +3363,10 @@
     <t>Livana Connect (ex-Sophie)</t>
   </si>
   <si>
-    <t>nicolasraulin22@gmail.com | linkedin.com/in/nicolas-raulin-8905aa27b</t>
+    <t>contact@livanaconnect.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/livana-connect/</t>
   </si>
   <si>
     <t>Nicolas Raulin</t>
@@ -3246,7 +3381,10 @@
     <t>PAYP</t>
   </si>
   <si>
-    <t>linkedin.com/company/payp-immobilier-entreprise | linkedin.com/in/mathilde-girardot00</t>
+    <t>contact@payp.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/payp-immobilier-entreprise/?originalSubdomain=fr</t>
   </si>
   <si>
     <t>Mathilde Girardot, Esteban Boudalia, Armand Franas</t>
@@ -3258,7 +3396,7 @@
     <t>MonInspection.fr</t>
   </si>
   <si>
-    <t>linkedin.com/company/moninspection</t>
+    <t>https://www.linkedin.com/company/moninspection/</t>
   </si>
   <si>
     <t>Benjamin Guilbert, Driss Poncet</t>
@@ -3282,7 +3420,10 @@
     <t>Anim&amp;moi</t>
   </si>
   <si>
-    <t>non public – formulaire sur vg2dpharma.com (à vérifier)</t>
+    <t>contact.animetmoi@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/delforge-emeline-animetmoi/</t>
   </si>
   <si>
     <t>Romuald Schaeffer</t>
@@ -3297,7 +3438,10 @@
     <t>ELIDREO (ex-Bioversight)</t>
   </si>
   <si>
-    <t>linkedin.com/in/audrey-catteau-48929217b</t>
+    <t>contact@elidreo.com ELIDREO Chemin des Rouliers 51100 - Reims - France Horaires Du lundi au vendredi de 9h00 à 17h30  Nous suivre</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/elidreo/</t>
   </si>
   <si>
     <t>Audrey Catteau</t>
@@ -3321,7 +3465,10 @@
     <t>Databiotechnology</t>
   </si>
   <si>
-    <t>linkedin.com/in/pierre-darme | linkedin.com/in/marion-gagneux-lantreibecq-334662a8</t>
+    <t>contact@databiotechnology.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/databiotechnology/?originalSubdomain=fr</t>
   </si>
   <si>
     <t>Pierre Darme, Marion Gagneux-Lantreibecq</t>
@@ -3342,7 +3489,10 @@
     <t>Goodforest</t>
   </si>
   <si>
-    <t>linkedin.com/company/goodforest | linkedin.com/in/s%C3%A9bastien-connesson</t>
+    <t>contact@goodforest.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/goodforest/?originalSubdomain=fr</t>
   </si>
   <si>
     <t>Sébastien Connesson</t>
@@ -3354,6 +3504,12 @@
     <t>My Racing Coach</t>
   </si>
   <si>
+    <t>"contact@myracingcoach.com" &lt;contact@myracingcoach.com&gt;</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/myracingcoach/</t>
+  </si>
+  <si>
     <t>SportsTech - Suivi global des pilotes : physique, mental, data et sponsoring</t>
   </si>
   <si>
@@ -3369,12 +3525,21 @@
     <t>Futurail</t>
   </si>
   <si>
+    <t>info@futurail.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/futurail/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Transport/Rail - Solutions d automatisation pour la conduite ferroviaire</t>
   </si>
   <si>
     <t>Asterion Robotics</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/asterion-robotics/</t>
+  </si>
+  <si>
     <t>DeepTech/Robotique - Systèmes robotiques avancés issus de la recherche académique</t>
   </si>
   <si>
@@ -3387,6 +3552,12 @@
     <t>DFENSE LAB</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/dfense-lab/</t>
+  </si>
+  <si>
+    <t>contact@dfense-lab.com</t>
+  </si>
+  <si>
     <t>Cybersécurité - SOC combinant expertise humaine et technologies de pointe pour protéger les ETI</t>
   </si>
   <si>
@@ -3399,16 +3570,31 @@
     <t>EveryParts</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/everyparts/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>E-commerce/Data - Optimisation de pièces détachées via data et SEO</t>
   </si>
   <si>
     <t>WeClose</t>
   </si>
   <si>
+    <t>cyril.barthelme@we-close.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/weclosefrance/</t>
+  </si>
+  <si>
     <t>PropTech - Plateforme transactionnelle digitale pour l immobilier</t>
   </si>
   <si>
     <t>Krewzer</t>
+  </si>
+  <si>
+    <t>david@krewger.com</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/krewger/?originalSubdomain=fr</t>
   </si>
   <si>
     <t>MusicTech - Intelligence collective pour la découverte musicale et le soutien aux artistes</t>
@@ -4006,7 +4192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -4031,6 +4217,9 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5646,1268 +5835,1420 @@
       <c r="L52" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="B53" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>987</v>
+      </c>
       <c r="D53" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L53" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+        <v>993</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>995</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L54" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+        <v>998</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>1000</v>
+      </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L55" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+        <v>1003</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1005</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L56" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+        <v>1008</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1010</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L57" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+        <v>1013</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1015</v>
+      </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L58" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+        <v>1017</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1019</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L59" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="1"/>
+      <c r="A60" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="B60" s="1" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+        <v>1021</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1023</v>
+      </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L60" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="1"/>
+      <c r="A61" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B61" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>1025</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1026</v>
+      </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>1011</v>
+        <v>1027</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L61" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+        <v>1029</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>1031</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>1014</v>
+        <v>1032</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L62" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="1"/>
+      <c r="A63" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B63" s="1" t="s">
-        <v>1015</v>
+        <v>1033</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L63" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+        <v>1035</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1037</v>
+      </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>1018</v>
+        <v>1038</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L64" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="1"/>
+      <c r="A65" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B65" s="1" t="s">
-        <v>1019</v>
+        <v>1039</v>
       </c>
       <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="D65" s="1" t="s">
+        <v>1040</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L65" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="1"/>
+      <c r="A66" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B66" s="1" t="s">
-        <v>1021</v>
+        <v>1042</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L66" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>1023</v>
+        <v>1044</v>
       </c>
       <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>1024</v>
+        <v>1046</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L67" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+        <v>1047</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>1049</v>
+      </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>1026</v>
+        <v>1050</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L68" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
-        <v>1027</v>
+        <v>1051</v>
       </c>
       <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>1012</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L69" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
+        <v>1054</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>1056</v>
+      </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L70" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
+        <v>1058</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>1060</v>
+      </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L71" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
+        <v>1062</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>1064</v>
+      </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>1034</v>
+        <v>1065</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L72" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="1"/>
+      <c r="A73" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B73" s="1" t="s">
-        <v>1035</v>
+        <v>1066</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>1036</v>
+        <v>1067</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L73" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="1"/>
+      <c r="A74" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B74" s="1" t="s">
-        <v>1037</v>
+        <v>1068</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
-        <v>1038</v>
+        <v>1069</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L74" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
+        <v>1070</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>1040</v>
+        <v>1073</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L75" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
+        <v>1074</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>1072</v>
+      </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>1042</v>
+        <v>1076</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L76" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
+        <v>1077</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>1079</v>
+      </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>1044</v>
+        <v>1080</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L77" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
-        <v>1045</v>
+        <v>1081</v>
       </c>
       <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
+      <c r="D78" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>1046</v>
+        <v>1083</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L78" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
+        <v>1084</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>1086</v>
+      </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L79" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
+        <v>1088</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>1090</v>
+      </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1" t="s">
-        <v>1050</v>
+        <v>1091</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L80" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C81" s="1"/>
+        <v>1092</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1093</v>
+      </c>
       <c r="D81" s="1" t="s">
-        <v>1052</v>
+        <v>1094</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1053</v>
+        <v>1095</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1054</v>
+        <v>1096</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>1058</v>
+        <v>1100</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C82" s="1"/>
+        <v>1101</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1102</v>
+      </c>
       <c r="D82" s="1" t="s">
-        <v>1060</v>
+        <v>1103</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1061</v>
+        <v>1104</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1062</v>
+        <v>1105</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>1063</v>
+        <v>1106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B83" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1" t="s">
-        <v>1065</v>
+        <v>1107</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>1109</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1066</v>
+        <v>1110</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1067</v>
+        <v>1111</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>1063</v>
+        <v>1106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C84" s="1"/>
+        <v>1112</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>1113</v>
+      </c>
       <c r="D84" s="1" t="s">
-        <v>1069</v>
+        <v>1114</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1070</v>
+        <v>1115</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1071</v>
+        <v>1116</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>1072</v>
+        <v>1117</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C85" s="1"/>
+        <v>1118</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1119</v>
+      </c>
       <c r="D85" s="1" t="s">
-        <v>1074</v>
+        <v>1120</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1075</v>
+        <v>1121</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1076</v>
+        <v>1122</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>1063</v>
+        <v>1106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
-        <v>1077</v>
+        <v>1123</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>1078</v>
+        <v>1124</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1079</v>
+        <v>1125</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>1063</v>
+        <v>1106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="1"/>
+      <c r="A87" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B87" s="1" t="s">
-        <v>1081</v>
+        <v>1127</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1" t="s">
-        <v>1082</v>
+        <v>1128</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1083</v>
+        <v>1129</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1084</v>
+        <v>1130</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>1063</v>
+        <v>1106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C88" s="1"/>
+        <v>1131</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1132</v>
+      </c>
       <c r="D88" s="1" t="s">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1087</v>
+        <v>1134</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1055</v>
+        <v>1097</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1" t="s">
-        <v>1056</v>
+        <v>1098</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>1057</v>
+        <v>1099</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>1089</v>
+        <v>1136</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C89" s="1"/>
+        <v>1137</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1138</v>
+      </c>
       <c r="D89" s="1" t="s">
-        <v>1091</v>
+        <v>1139</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1092</v>
+        <v>1140</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1093</v>
+        <v>1141</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1094</v>
+        <v>1142</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1" t="s">
-        <v>1095</v>
+        <v>1143</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>1096</v>
+        <v>1144</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1097</v>
+        <v>1145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C90" s="1"/>
+        <v>1146</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>1147</v>
+      </c>
       <c r="D90" s="1" t="s">
-        <v>1099</v>
+        <v>1148</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1100</v>
+        <v>1149</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1101</v>
+        <v>1150</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1094</v>
+        <v>1142</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>1095</v>
+        <v>1143</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>1096</v>
+        <v>1144</v>
       </c>
       <c r="L90" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="1"/>
+      <c r="A91" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B91" s="1" t="s">
-        <v>1102</v>
+        <v>1151</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>1103</v>
+        <v>1152</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1104</v>
+        <v>1153</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1094</v>
+        <v>1142</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1" t="s">
-        <v>1095</v>
+        <v>1143</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>1096</v>
+        <v>1144</v>
       </c>
       <c r="L91" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C92" s="1"/>
+        <v>1154</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1155</v>
+      </c>
       <c r="D92" s="1" t="s">
-        <v>1106</v>
+        <v>1156</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1107</v>
+        <v>1157</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1108</v>
+        <v>1158</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1094</v>
+        <v>1142</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>1095</v>
+        <v>1143</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>1096</v>
+        <v>1144</v>
       </c>
       <c r="L92" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="1"/>
       <c r="B93" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+        <v>1159</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>1161</v>
+      </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>1110</v>
+        <v>1162</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L93" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+        <v>1166</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1168</v>
+      </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>1115</v>
+        <v>1169</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L94" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>1171</v>
+      </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>1117</v>
+        <v>1172</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L95" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="1"/>
+      <c r="A96" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B96" s="1" t="s">
-        <v>1118</v>
+        <v>1173</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1" t="s">
-        <v>1119</v>
+        <v>1174</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L96" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+        <v>1175</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>1177</v>
+      </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1" t="s">
-        <v>1121</v>
+        <v>1178</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L97" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="1"/>
+      <c r="A98" s="1" t="s">
+        <v>861</v>
+      </c>
       <c r="B98" s="1" t="s">
-        <v>1122</v>
+        <v>1179</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1" t="s">
-        <v>1123</v>
+        <v>1180</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L98" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
-        <v>1124</v>
+        <v>1181</v>
       </c>
       <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="D99" s="1" t="s">
+        <v>1182</v>
+      </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1" t="s">
-        <v>1125</v>
+        <v>1183</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L99" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+        <v>1184</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1186</v>
+      </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1" t="s">
-        <v>1127</v>
+        <v>1187</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L100" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+        <v>1188</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>1190</v>
+      </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1" t="s">
-        <v>1129</v>
+        <v>1191</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L101" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
-        <v>1130</v>
+        <v>1192</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1" t="s">
-        <v>1131</v>
+        <v>1193</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1111</v>
+        <v>1163</v>
       </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1" t="s">
-        <v>1112</v>
+        <v>1164</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>1113</v>
+        <v>1165</v>
       </c>
       <c r="L102" s="1"/>
     </row>
@@ -12486,13 +12827,13 @@
     <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="18.75">
       <c r="A501" s="1"/>
       <c r="B501" s="1" t="s">
-        <v>1132</v>
+        <v>1194</v>
       </c>
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
       <c r="F501" s="1" t="s">
-        <v>1133</v>
+        <v>1195</v>
       </c>
       <c r="G501" s="1"/>
       <c r="H501" s="1"/>
@@ -12506,13 +12847,13 @@
     <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="18.75">
       <c r="A502" s="1"/>
       <c r="B502" s="1" t="s">
-        <v>1134</v>
+        <v>1196</v>
       </c>
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
       <c r="F502" s="1" t="s">
-        <v>1135</v>
+        <v>1197</v>
       </c>
       <c r="G502" s="1"/>
       <c r="H502" s="1"/>
@@ -12526,13 +12867,13 @@
     <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="18.75">
       <c r="A503" s="1"/>
       <c r="B503" s="1" t="s">
-        <v>1136</v>
+        <v>1198</v>
       </c>
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
       <c r="F503" s="1" t="s">
-        <v>1137</v>
+        <v>1199</v>
       </c>
       <c r="G503" s="1"/>
       <c r="H503" s="1"/>
@@ -12546,13 +12887,13 @@
     <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="18.75">
       <c r="A504" s="1"/>
       <c r="B504" s="1" t="s">
-        <v>1138</v>
+        <v>1200</v>
       </c>
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
       <c r="F504" s="1" t="s">
-        <v>1139</v>
+        <v>1201</v>
       </c>
       <c r="G504" s="1"/>
       <c r="H504" s="1"/>
@@ -12566,13 +12907,13 @@
     <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="18.75">
       <c r="A505" s="1"/>
       <c r="B505" s="1" t="s">
-        <v>1140</v>
+        <v>1202</v>
       </c>
       <c r="C505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
       <c r="F505" s="1" t="s">
-        <v>1141</v>
+        <v>1203</v>
       </c>
       <c r="G505" s="1"/>
       <c r="H505" s="1"/>
@@ -12586,13 +12927,13 @@
     <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="18.75">
       <c r="A506" s="1"/>
       <c r="B506" s="1" t="s">
-        <v>1142</v>
+        <v>1204</v>
       </c>
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
       <c r="F506" s="1" t="s">
-        <v>1143</v>
+        <v>1205</v>
       </c>
       <c r="G506" s="1"/>
       <c r="H506" s="1"/>
@@ -12606,13 +12947,13 @@
     <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="18.75">
       <c r="A507" s="1"/>
       <c r="B507" s="1" t="s">
-        <v>1144</v>
+        <v>1206</v>
       </c>
       <c r="C507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
       <c r="F507" s="1" t="s">
-        <v>1145</v>
+        <v>1207</v>
       </c>
       <c r="G507" s="1"/>
       <c r="H507" s="1"/>
@@ -12626,13 +12967,13 @@
     <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="18.75">
       <c r="A508" s="1"/>
       <c r="B508" s="1" t="s">
-        <v>1146</v>
+        <v>1208</v>
       </c>
       <c r="C508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
       <c r="F508" s="1" t="s">
-        <v>1147</v>
+        <v>1209</v>
       </c>
       <c r="G508" s="1"/>
       <c r="H508" s="1"/>
@@ -12646,13 +12987,13 @@
     <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18.75">
       <c r="A509" s="1"/>
       <c r="B509" s="1" t="s">
-        <v>1148</v>
+        <v>1210</v>
       </c>
       <c r="C509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
       <c r="F509" s="1" t="s">
-        <v>1149</v>
+        <v>1211</v>
       </c>
       <c r="G509" s="1"/>
       <c r="H509" s="1"/>
@@ -12666,13 +13007,13 @@
     <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="18.75">
       <c r="A510" s="1"/>
       <c r="B510" s="1" t="s">
-        <v>1150</v>
+        <v>1212</v>
       </c>
       <c r="C510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
       <c r="F510" s="1" t="s">
-        <v>1151</v>
+        <v>1213</v>
       </c>
       <c r="G510" s="1"/>
       <c r="H510" s="1"/>
@@ -12686,16 +13027,16 @@
     <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="18.75">
       <c r="A511" s="1"/>
       <c r="B511" s="1" t="s">
-        <v>1152</v>
+        <v>1214</v>
       </c>
       <c r="C511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
       <c r="F511" s="1" t="s">
-        <v>1153</v>
+        <v>1215</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>1154</v>
+        <v>1216</v>
       </c>
       <c r="H511" s="1"/>
       <c r="I511" s="1"/>
@@ -12708,13 +13049,13 @@
     <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="18.75">
       <c r="A512" s="1"/>
       <c r="B512" s="1" t="s">
-        <v>1155</v>
+        <v>1217</v>
       </c>
       <c r="C512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
       <c r="F512" s="1" t="s">
-        <v>1156</v>
+        <v>1218</v>
       </c>
       <c r="G512" s="1"/>
       <c r="H512" s="1"/>
@@ -12728,13 +13069,13 @@
     <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="18.75">
       <c r="A513" s="1"/>
       <c r="B513" s="1" t="s">
-        <v>1157</v>
+        <v>1219</v>
       </c>
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
       <c r="F513" s="1" t="s">
-        <v>1158</v>
+        <v>1220</v>
       </c>
       <c r="G513" s="1"/>
       <c r="H513" s="1"/>
@@ -12748,13 +13089,13 @@
     <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="18.75">
       <c r="A514" s="1"/>
       <c r="B514" s="1" t="s">
-        <v>1159</v>
+        <v>1221</v>
       </c>
       <c r="C514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
       <c r="F514" s="1" t="s">
-        <v>1160</v>
+        <v>1222</v>
       </c>
       <c r="G514" s="1"/>
       <c r="H514" s="1"/>
@@ -12768,13 +13109,13 @@
     <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="18.75">
       <c r="A515" s="1"/>
       <c r="B515" s="1" t="s">
-        <v>1161</v>
+        <v>1223</v>
       </c>
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
       <c r="F515" s="1" t="s">
-        <v>1162</v>
+        <v>1224</v>
       </c>
       <c r="G515" s="1"/>
       <c r="H515" s="1"/>
@@ -12788,13 +13129,13 @@
     <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="18.75">
       <c r="A516" s="1"/>
       <c r="B516" s="1" t="s">
-        <v>1163</v>
+        <v>1225</v>
       </c>
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
       <c r="F516" s="1" t="s">
-        <v>1164</v>
+        <v>1226</v>
       </c>
       <c r="G516" s="1"/>
       <c r="H516" s="1"/>
@@ -12808,13 +13149,13 @@
     <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="18.75">
       <c r="A517" s="1"/>
       <c r="B517" s="1" t="s">
-        <v>1165</v>
+        <v>1227</v>
       </c>
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
       <c r="F517" s="1" t="s">
-        <v>1166</v>
+        <v>1228</v>
       </c>
       <c r="G517" s="1"/>
       <c r="H517" s="1"/>
@@ -12828,13 +13169,13 @@
     <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18.75">
       <c r="A518" s="1"/>
       <c r="B518" s="1" t="s">
-        <v>1167</v>
+        <v>1229</v>
       </c>
       <c r="C518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
       <c r="F518" s="1" t="s">
-        <v>1162</v>
+        <v>1224</v>
       </c>
       <c r="G518" s="1"/>
       <c r="H518" s="1"/>
@@ -12848,13 +13189,13 @@
     <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="18.75">
       <c r="A519" s="1"/>
       <c r="B519" s="1" t="s">
-        <v>1168</v>
+        <v>1230</v>
       </c>
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
       <c r="F519" s="1" t="s">
-        <v>1169</v>
+        <v>1231</v>
       </c>
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
@@ -12868,13 +13209,13 @@
     <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="18.75">
       <c r="A520" s="1"/>
       <c r="B520" s="1" t="s">
-        <v>1170</v>
+        <v>1232</v>
       </c>
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
       <c r="F520" s="1" t="s">
-        <v>1171</v>
+        <v>1233</v>
       </c>
       <c r="G520" s="1"/>
       <c r="H520" s="1"/>
@@ -12888,13 +13229,13 @@
     <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="18.75">
       <c r="A521" s="1"/>
       <c r="B521" s="1" t="s">
-        <v>1172</v>
+        <v>1234</v>
       </c>
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
       <c r="F521" s="1" t="s">
-        <v>1173</v>
+        <v>1235</v>
       </c>
       <c r="G521" s="1"/>
       <c r="H521" s="1"/>
@@ -12908,13 +13249,13 @@
     <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="18.75">
       <c r="A522" s="1"/>
       <c r="B522" s="1" t="s">
-        <v>1174</v>
+        <v>1236</v>
       </c>
       <c r="C522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
       <c r="F522" s="1" t="s">
-        <v>1175</v>
+        <v>1237</v>
       </c>
       <c r="G522" s="1"/>
       <c r="H522" s="1"/>
@@ -12928,16 +13269,16 @@
     <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="18.75">
       <c r="A523" s="1"/>
       <c r="B523" s="1" t="s">
-        <v>1176</v>
+        <v>1238</v>
       </c>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
       <c r="F523" s="1" t="s">
-        <v>1177</v>
+        <v>1239</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>1178</v>
+        <v>1240</v>
       </c>
       <c r="H523" s="1"/>
       <c r="I523" s="1"/>
@@ -12950,13 +13291,13 @@
     <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="18.75">
       <c r="A524" s="1"/>
       <c r="B524" s="1" t="s">
-        <v>1179</v>
+        <v>1241</v>
       </c>
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
       <c r="F524" s="1" t="s">
-        <v>1180</v>
+        <v>1242</v>
       </c>
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
@@ -12970,13 +13311,13 @@
     <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="18.75">
       <c r="A525" s="1"/>
       <c r="B525" s="1" t="s">
-        <v>1181</v>
+        <v>1243</v>
       </c>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
       <c r="F525" s="1" t="s">
-        <v>1182</v>
+        <v>1244</v>
       </c>
       <c r="G525" s="1"/>
       <c r="H525" s="1"/>
@@ -12990,16 +13331,16 @@
     <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="18.75">
       <c r="A526" s="1"/>
       <c r="B526" s="1" t="s">
-        <v>1183</v>
+        <v>1245</v>
       </c>
       <c r="C526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
       <c r="F526" s="1" t="s">
-        <v>1184</v>
+        <v>1246</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>1154</v>
+        <v>1216</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -13012,16 +13353,16 @@
     <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="18.75">
       <c r="A527" s="1"/>
       <c r="B527" s="1" t="s">
-        <v>1185</v>
+        <v>1247</v>
       </c>
       <c r="C527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
       <c r="F527" s="1" t="s">
-        <v>1186</v>
+        <v>1248</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>1187</v>
+        <v>1249</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -13034,13 +13375,13 @@
     <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="18.75">
       <c r="A528" s="1"/>
       <c r="B528" s="1" t="s">
-        <v>1188</v>
+        <v>1250</v>
       </c>
       <c r="C528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
       <c r="F528" s="1" t="s">
-        <v>1189</v>
+        <v>1251</v>
       </c>
       <c r="G528" s="1"/>
       <c r="H528" s="1"/>
@@ -13054,13 +13395,13 @@
     <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="18.75">
       <c r="A529" s="1"/>
       <c r="B529" s="1" t="s">
-        <v>1190</v>
+        <v>1252</v>
       </c>
       <c r="C529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
       <c r="F529" s="1" t="s">
-        <v>1191</v>
+        <v>1253</v>
       </c>
       <c r="G529" s="1"/>
       <c r="H529" s="1"/>
@@ -13074,1144 +13415,1144 @@
     <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="18.75">
       <c r="A530" s="1"/>
       <c r="B530" s="1" t="s">
-        <v>1192</v>
+        <v>1254</v>
       </c>
       <c r="C530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
       <c r="F530" s="1" t="s">
-        <v>1193</v>
+        <v>1255</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>1194</v>
+        <v>1256</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
       <c r="J530" s="1" t="s">
-        <v>1195</v>
+        <v>1257</v>
       </c>
       <c r="K530" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L530" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="18.75">
       <c r="A531" s="1"/>
       <c r="B531" s="1" t="s">
-        <v>1197</v>
+        <v>1259</v>
       </c>
       <c r="C531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
       <c r="F531" s="1" t="s">
-        <v>1198</v>
+        <v>1260</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>1199</v>
+        <v>1261</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
       <c r="J531" s="1" t="s">
-        <v>1200</v>
+        <v>1262</v>
       </c>
       <c r="K531" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L531" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="18.75">
       <c r="A532" s="1"/>
       <c r="B532" s="1" t="s">
-        <v>1201</v>
+        <v>1263</v>
       </c>
       <c r="C532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
       <c r="F532" s="1" t="s">
-        <v>1202</v>
+        <v>1264</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>1203</v>
+        <v>1265</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
       <c r="J532" s="1" t="s">
-        <v>1204</v>
+        <v>1266</v>
       </c>
       <c r="K532" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L532" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="18.75">
       <c r="A533" s="1"/>
       <c r="B533" s="1" t="s">
-        <v>1205</v>
+        <v>1267</v>
       </c>
       <c r="C533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
       <c r="F533" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G533" s="1"/>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
       <c r="J533" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K533" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L533" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="18.75">
       <c r="A534" s="1"/>
       <c r="B534" s="1" t="s">
-        <v>1208</v>
+        <v>1270</v>
       </c>
       <c r="C534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
       <c r="F534" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G534" s="1"/>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
       <c r="J534" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K534" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L534" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="18.75">
       <c r="A535" s="1"/>
       <c r="B535" s="1" t="s">
-        <v>1209</v>
+        <v>1271</v>
       </c>
       <c r="C535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
       <c r="F535" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G535" s="1"/>
       <c r="H535" s="1"/>
       <c r="I535" s="1"/>
       <c r="J535" s="1" t="s">
-        <v>1210</v>
+        <v>1272</v>
       </c>
       <c r="K535" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L535" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="18.75">
       <c r="A536" s="1"/>
       <c r="B536" s="1" t="s">
-        <v>1211</v>
+        <v>1273</v>
       </c>
       <c r="C536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
       <c r="F536" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G536" s="1"/>
       <c r="H536" s="1"/>
       <c r="I536" s="1"/>
       <c r="J536" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K536" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L536" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="18.75">
       <c r="A537" s="1"/>
       <c r="B537" s="1" t="s">
-        <v>1212</v>
+        <v>1274</v>
       </c>
       <c r="C537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
       <c r="F537" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G537" s="1"/>
       <c r="H537" s="1"/>
       <c r="I537" s="1"/>
       <c r="J537" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K537" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L537" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="18.75">
       <c r="A538" s="1"/>
       <c r="B538" s="1" t="s">
-        <v>1213</v>
+        <v>1275</v>
       </c>
       <c r="C538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
       <c r="F538" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G538" s="1"/>
       <c r="H538" s="1"/>
       <c r="I538" s="1"/>
       <c r="J538" s="1" t="s">
-        <v>1214</v>
+        <v>1276</v>
       </c>
       <c r="K538" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L538" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="18.75">
       <c r="A539" s="1"/>
       <c r="B539" s="1" t="s">
-        <v>1215</v>
+        <v>1277</v>
       </c>
       <c r="C539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
       <c r="F539" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G539" s="1"/>
       <c r="H539" s="1"/>
       <c r="I539" s="1"/>
       <c r="J539" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K539" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L539" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="18.75">
       <c r="A540" s="1"/>
       <c r="B540" s="1" t="s">
-        <v>1216</v>
+        <v>1278</v>
       </c>
       <c r="C540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
       <c r="F540" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G540" s="1"/>
       <c r="H540" s="1"/>
       <c r="I540" s="1"/>
       <c r="J540" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K540" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L540" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="18.75">
       <c r="A541" s="1"/>
       <c r="B541" s="1" t="s">
-        <v>1217</v>
+        <v>1279</v>
       </c>
       <c r="C541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
       <c r="F541" s="1" t="s">
-        <v>1206</v>
+        <v>1268</v>
       </c>
       <c r="G541" s="1"/>
       <c r="H541" s="1"/>
       <c r="I541" s="1"/>
       <c r="J541" s="1" t="s">
-        <v>1207</v>
+        <v>1269</v>
       </c>
       <c r="K541" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L541" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="18.75">
       <c r="A542" s="1"/>
       <c r="B542" s="1" t="s">
-        <v>1218</v>
+        <v>1280</v>
       </c>
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
       <c r="F542" s="1" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="G542" s="1"/>
       <c r="H542" s="1"/>
       <c r="I542" s="1"/>
       <c r="J542" s="1" t="s">
-        <v>1220</v>
+        <v>1282</v>
       </c>
       <c r="K542" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L542" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="18.75">
       <c r="A543" s="1"/>
       <c r="B543" s="1" t="s">
-        <v>1221</v>
+        <v>1283</v>
       </c>
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
       <c r="F543" s="1" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="G543" s="1"/>
       <c r="H543" s="1"/>
       <c r="I543" s="1"/>
       <c r="J543" s="1" t="s">
-        <v>1222</v>
+        <v>1284</v>
       </c>
       <c r="K543" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L543" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="18.75">
       <c r="A544" s="1"/>
       <c r="B544" s="1" t="s">
-        <v>1223</v>
+        <v>1285</v>
       </c>
       <c r="C544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
       <c r="F544" s="1" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="G544" s="1"/>
       <c r="H544" s="1"/>
       <c r="I544" s="1"/>
       <c r="J544" s="1" t="s">
-        <v>1222</v>
+        <v>1284</v>
       </c>
       <c r="K544" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L544" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="18.75">
       <c r="A545" s="1"/>
       <c r="B545" s="1" t="s">
-        <v>1224</v>
+        <v>1286</v>
       </c>
       <c r="C545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
       <c r="F545" s="1" t="s">
-        <v>1219</v>
+        <v>1281</v>
       </c>
       <c r="G545" s="1"/>
       <c r="H545" s="1"/>
       <c r="I545" s="1"/>
       <c r="J545" s="1" t="s">
-        <v>1222</v>
+        <v>1284</v>
       </c>
       <c r="K545" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L545" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="18.75">
       <c r="A546" s="1"/>
       <c r="B546" s="1" t="s">
-        <v>1225</v>
+        <v>1287</v>
       </c>
       <c r="C546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
       <c r="F546" s="1" t="s">
-        <v>1226</v>
+        <v>1288</v>
       </c>
       <c r="G546" s="1"/>
       <c r="H546" s="1"/>
       <c r="I546" s="1"/>
       <c r="J546" s="1" t="s">
-        <v>1227</v>
+        <v>1289</v>
       </c>
       <c r="K546" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L546" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="18.75">
       <c r="A547" s="1"/>
       <c r="B547" s="1" t="s">
-        <v>1228</v>
+        <v>1290</v>
       </c>
       <c r="C547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
       <c r="F547" s="1" t="s">
-        <v>1226</v>
+        <v>1288</v>
       </c>
       <c r="G547" s="1"/>
       <c r="H547" s="1"/>
       <c r="I547" s="1"/>
       <c r="J547" s="1" t="s">
-        <v>1227</v>
+        <v>1289</v>
       </c>
       <c r="K547" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L547" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="18.75">
       <c r="A548" s="1"/>
       <c r="B548" s="1" t="s">
-        <v>1229</v>
+        <v>1291</v>
       </c>
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
       <c r="F548" s="1" t="s">
-        <v>1226</v>
+        <v>1288</v>
       </c>
       <c r="G548" s="1"/>
       <c r="H548" s="1"/>
       <c r="I548" s="1"/>
       <c r="J548" s="1" t="s">
-        <v>1227</v>
+        <v>1289</v>
       </c>
       <c r="K548" s="1" t="s">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="L548" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="18.75">
       <c r="A549" s="1"/>
       <c r="B549" s="1" t="s">
-        <v>1230</v>
+        <v>1292</v>
       </c>
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
       <c r="F549" s="1" t="s">
-        <v>1231</v>
+        <v>1293</v>
       </c>
       <c r="G549" s="1" t="s">
-        <v>1232</v>
+        <v>1294</v>
       </c>
       <c r="H549" s="1"/>
       <c r="I549" s="1"/>
       <c r="J549" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K549" s="1" t="s">
-        <v>1234</v>
+        <v>1296</v>
       </c>
       <c r="L549" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="18.75">
       <c r="A550" s="1"/>
       <c r="B550" s="1" t="s">
-        <v>1235</v>
+        <v>1297</v>
       </c>
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
       <c r="F550" s="1" t="s">
-        <v>1236</v>
+        <v>1298</v>
       </c>
       <c r="G550" s="1" t="s">
-        <v>1232</v>
+        <v>1294</v>
       </c>
       <c r="H550" s="1"/>
       <c r="I550" s="1"/>
       <c r="J550" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K550" s="1" t="s">
-        <v>1234</v>
+        <v>1296</v>
       </c>
       <c r="L550" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="18.75">
       <c r="A551" s="1"/>
       <c r="B551" s="1" t="s">
-        <v>1237</v>
+        <v>1299</v>
       </c>
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
       <c r="F551" s="1" t="s">
-        <v>1238</v>
+        <v>1300</v>
       </c>
       <c r="G551" s="1" t="s">
-        <v>1232</v>
+        <v>1294</v>
       </c>
       <c r="H551" s="1"/>
       <c r="I551" s="1"/>
       <c r="J551" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K551" s="1" t="s">
-        <v>1234</v>
+        <v>1296</v>
       </c>
       <c r="L551" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="18.75">
       <c r="A552" s="1"/>
       <c r="B552" s="1" t="s">
-        <v>1239</v>
+        <v>1301</v>
       </c>
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
       <c r="F552" s="1" t="s">
-        <v>1240</v>
+        <v>1302</v>
       </c>
       <c r="G552" s="1" t="s">
-        <v>1241</v>
+        <v>1303</v>
       </c>
       <c r="H552" s="1"/>
       <c r="I552" s="1"/>
       <c r="J552" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K552" s="1" t="s">
-        <v>1242</v>
+        <v>1304</v>
       </c>
       <c r="L552" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="18.75">
       <c r="A553" s="1"/>
       <c r="B553" s="1" t="s">
-        <v>1243</v>
+        <v>1305</v>
       </c>
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
       <c r="F553" s="1" t="s">
-        <v>1244</v>
+        <v>1306</v>
       </c>
       <c r="G553" s="1" t="s">
-        <v>1241</v>
+        <v>1303</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
       <c r="J553" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K553" s="1" t="s">
-        <v>1234</v>
+        <v>1296</v>
       </c>
       <c r="L553" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="18.75">
       <c r="A554" s="1"/>
       <c r="B554" s="1" t="s">
-        <v>1245</v>
+        <v>1307</v>
       </c>
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
       <c r="F554" s="1" t="s">
-        <v>1246</v>
+        <v>1308</v>
       </c>
       <c r="G554" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
       <c r="J554" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K554" s="1" t="s">
-        <v>1248</v>
+        <v>1310</v>
       </c>
       <c r="L554" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="18.75">
       <c r="A555" s="1"/>
       <c r="B555" s="1" t="s">
-        <v>1249</v>
+        <v>1311</v>
       </c>
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
       <c r="F555" s="1" t="s">
-        <v>1250</v>
+        <v>1312</v>
       </c>
       <c r="G555" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
       <c r="J555" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K555" s="1" t="s">
-        <v>1248</v>
+        <v>1310</v>
       </c>
       <c r="L555" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="18.75">
       <c r="A556" s="1"/>
       <c r="B556" s="1" t="s">
-        <v>1251</v>
+        <v>1313</v>
       </c>
       <c r="C556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
       <c r="F556" s="1" t="s">
-        <v>1252</v>
+        <v>1314</v>
       </c>
       <c r="G556" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
       <c r="J556" s="1" t="s">
-        <v>1233</v>
+        <v>1295</v>
       </c>
       <c r="K556" s="1" t="s">
-        <v>1253</v>
+        <v>1315</v>
       </c>
       <c r="L556" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="18.75">
       <c r="A557" s="1"/>
       <c r="B557" s="1" t="s">
-        <v>1254</v>
+        <v>1316</v>
       </c>
       <c r="C557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
       <c r="F557" s="1" t="s">
-        <v>1255</v>
+        <v>1317</v>
       </c>
       <c r="G557" s="1" t="s">
-        <v>1256</v>
+        <v>1318</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
       <c r="J557" s="1" t="s">
-        <v>1257</v>
+        <v>1319</v>
       </c>
       <c r="K557" s="1" t="s">
-        <v>1258</v>
+        <v>1320</v>
       </c>
       <c r="L557" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="18.75">
       <c r="A558" s="1"/>
       <c r="B558" s="1" t="s">
-        <v>1259</v>
+        <v>1321</v>
       </c>
       <c r="C558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
       <c r="F558" s="1" t="s">
-        <v>1260</v>
+        <v>1322</v>
       </c>
       <c r="G558" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
       <c r="J558" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K558" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L558" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="18.75">
       <c r="A559" s="1"/>
       <c r="B559" s="1" t="s">
-        <v>1263</v>
+        <v>1325</v>
       </c>
       <c r="C559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
       <c r="F559" s="1" t="s">
-        <v>1264</v>
+        <v>1326</v>
       </c>
       <c r="G559" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
       <c r="J559" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K559" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L559" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="18.75">
       <c r="A560" s="1"/>
       <c r="B560" s="1" t="s">
-        <v>1265</v>
+        <v>1327</v>
       </c>
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
       <c r="F560" s="1" t="s">
-        <v>1266</v>
+        <v>1328</v>
       </c>
       <c r="G560" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
       <c r="J560" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K560" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L560" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="18.75">
       <c r="A561" s="1"/>
       <c r="B561" s="1" t="s">
-        <v>1267</v>
+        <v>1329</v>
       </c>
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
       <c r="F561" s="1" t="s">
-        <v>1268</v>
+        <v>1330</v>
       </c>
       <c r="G561" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
       <c r="J561" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K561" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L561" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="18.75">
       <c r="A562" s="1"/>
       <c r="B562" s="1" t="s">
-        <v>1269</v>
+        <v>1331</v>
       </c>
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
       <c r="F562" s="1" t="s">
-        <v>1270</v>
+        <v>1332</v>
       </c>
       <c r="G562" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
       <c r="J562" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K562" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L562" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="18.75">
       <c r="A563" s="1"/>
       <c r="B563" s="1" t="s">
-        <v>1271</v>
+        <v>1333</v>
       </c>
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
       <c r="F563" s="1" t="s">
-        <v>1272</v>
+        <v>1334</v>
       </c>
       <c r="G563" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1"/>
       <c r="J563" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K563" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L563" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="18.75">
       <c r="A564" s="1"/>
       <c r="B564" s="1" t="s">
-        <v>1273</v>
+        <v>1335</v>
       </c>
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
       <c r="F564" s="1" t="s">
-        <v>1274</v>
+        <v>1336</v>
       </c>
       <c r="G564" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H564" s="1"/>
       <c r="I564" s="1"/>
       <c r="J564" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K564" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L564" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="18.75">
       <c r="A565" s="1"/>
       <c r="B565" s="1" t="s">
-        <v>1275</v>
+        <v>1337</v>
       </c>
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
       <c r="F565" s="1" t="s">
-        <v>1276</v>
+        <v>1338</v>
       </c>
       <c r="G565" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H565" s="1"/>
       <c r="I565" s="1"/>
       <c r="J565" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K565" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L565" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="18.75">
       <c r="A566" s="1"/>
       <c r="B566" s="1" t="s">
-        <v>1277</v>
+        <v>1339</v>
       </c>
       <c r="C566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
       <c r="F566" s="1" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="G566" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H566" s="1"/>
       <c r="I566" s="1"/>
       <c r="J566" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K566" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L566" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="18.75">
       <c r="A567" s="1"/>
       <c r="B567" s="1" t="s">
-        <v>1279</v>
+        <v>1341</v>
       </c>
       <c r="C567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
       <c r="F567" s="1" t="s">
-        <v>1280</v>
+        <v>1342</v>
       </c>
       <c r="G567" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H567" s="1"/>
       <c r="I567" s="1"/>
       <c r="J567" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K567" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L567" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="18.75">
       <c r="A568" s="1"/>
       <c r="B568" s="1" t="s">
-        <v>1281</v>
+        <v>1343</v>
       </c>
       <c r="C568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
       <c r="F568" s="1" t="s">
-        <v>1282</v>
+        <v>1344</v>
       </c>
       <c r="G568" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H568" s="1"/>
       <c r="I568" s="1"/>
       <c r="J568" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K568" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L568" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="18.75">
       <c r="A569" s="1"/>
       <c r="B569" s="1" t="s">
-        <v>1283</v>
+        <v>1345</v>
       </c>
       <c r="C569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
       <c r="F569" s="1" t="s">
-        <v>1284</v>
+        <v>1346</v>
       </c>
       <c r="G569" s="1" t="s">
-        <v>1247</v>
+        <v>1309</v>
       </c>
       <c r="H569" s="1"/>
       <c r="I569" s="1"/>
       <c r="J569" s="1" t="s">
-        <v>1261</v>
+        <v>1323</v>
       </c>
       <c r="K569" s="1" t="s">
-        <v>1262</v>
+        <v>1324</v>
       </c>
       <c r="L569" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="18.75">
       <c r="A570" s="1"/>
       <c r="B570" s="1" t="s">
-        <v>1285</v>
+        <v>1347</v>
       </c>
       <c r="C570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
       <c r="F570" s="1" t="s">
-        <v>1286</v>
+        <v>1348</v>
       </c>
       <c r="G570" s="1" t="s">
-        <v>1287</v>
+        <v>1349</v>
       </c>
       <c r="H570" s="1"/>
       <c r="I570" s="1"/>
       <c r="J570" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K570" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L570" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="18.75">
       <c r="A571" s="1"/>
       <c r="B571" s="1" t="s">
-        <v>1290</v>
+        <v>1352</v>
       </c>
       <c r="C571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
       <c r="F571" s="1" t="s">
-        <v>1291</v>
+        <v>1353</v>
       </c>
       <c r="G571" s="1" t="s">
-        <v>1287</v>
+        <v>1349</v>
       </c>
       <c r="H571" s="1"/>
       <c r="I571" s="1"/>
       <c r="J571" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K571" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L571" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="18.75">
       <c r="A572" s="1"/>
       <c r="B572" s="1" t="s">
-        <v>1292</v>
+        <v>1354</v>
       </c>
       <c r="C572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
       <c r="F572" s="1" t="s">
-        <v>1293</v>
+        <v>1355</v>
       </c>
       <c r="G572" s="1" t="s">
-        <v>1294</v>
+        <v>1356</v>
       </c>
       <c r="H572" s="1"/>
       <c r="I572" s="1"/>
       <c r="J572" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K572" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L572" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="18.75">
       <c r="A573" s="1"/>
       <c r="B573" s="1" t="s">
-        <v>1295</v>
+        <v>1357</v>
       </c>
       <c r="C573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
       <c r="F573" s="1" t="s">
-        <v>1296</v>
+        <v>1358</v>
       </c>
       <c r="G573" s="1" t="s">
-        <v>1294</v>
+        <v>1356</v>
       </c>
       <c r="H573" s="1"/>
       <c r="I573" s="1"/>
       <c r="J573" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K573" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L573" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="18.75">
       <c r="A574" s="1"/>
       <c r="B574" s="1" t="s">
-        <v>1297</v>
+        <v>1359</v>
       </c>
       <c r="C574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
       <c r="F574" s="1" t="s">
-        <v>1298</v>
+        <v>1360</v>
       </c>
       <c r="G574" s="1" t="s">
-        <v>1294</v>
+        <v>1356</v>
       </c>
       <c r="H574" s="1"/>
       <c r="I574" s="1"/>
       <c r="J574" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K574" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L574" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="18.75">
       <c r="A575" s="1"/>
       <c r="B575" s="1" t="s">
-        <v>1299</v>
+        <v>1361</v>
       </c>
       <c r="C575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
       <c r="F575" s="1" t="s">
-        <v>1298</v>
+        <v>1360</v>
       </c>
       <c r="G575" s="1" t="s">
-        <v>1294</v>
+        <v>1356</v>
       </c>
       <c r="H575" s="1"/>
       <c r="I575" s="1"/>
       <c r="J575" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K575" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L575" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="18.75">
       <c r="A576" s="1"/>
       <c r="B576" s="1" t="s">
-        <v>1300</v>
+        <v>1362</v>
       </c>
       <c r="C576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
       <c r="F576" s="1" t="s">
-        <v>1298</v>
+        <v>1360</v>
       </c>
       <c r="G576" s="1" t="s">
-        <v>1294</v>
+        <v>1356</v>
       </c>
       <c r="H576" s="1"/>
       <c r="I576" s="1"/>
       <c r="J576" s="1" t="s">
-        <v>1288</v>
+        <v>1350</v>
       </c>
       <c r="K576" s="1" t="s">
-        <v>1289</v>
+        <v>1351</v>
       </c>
       <c r="L576" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="18.75">
       <c r="A577" s="1"/>
       <c r="B577" s="1" t="s">
-        <v>1301</v>
+        <v>1363</v>
       </c>
       <c r="C577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
       <c r="F577" s="1" t="s">
-        <v>1302</v>
+        <v>1364</v>
       </c>
       <c r="G577" s="1" t="s">
-        <v>1241</v>
+        <v>1303</v>
       </c>
       <c r="H577" s="1"/>
       <c r="I577" s="1"/>
       <c r="J577" s="1" t="s">
-        <v>1303</v>
+        <v>1365</v>
       </c>
       <c r="K577" s="1" t="s">
-        <v>1304</v>
+        <v>1366</v>
       </c>
       <c r="L577" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="18.75">
       <c r="A578" s="1"/>
       <c r="B578" s="1" t="s">
-        <v>1305</v>
+        <v>1367</v>
       </c>
       <c r="C578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
       <c r="F578" s="1" t="s">
-        <v>1306</v>
+        <v>1368</v>
       </c>
       <c r="G578" s="1" t="s">
-        <v>1241</v>
+        <v>1303</v>
       </c>
       <c r="H578" s="1"/>
       <c r="I578" s="1"/>
       <c r="J578" s="1" t="s">
-        <v>1303</v>
+        <v>1365</v>
       </c>
       <c r="K578" s="1" t="s">
-        <v>1304</v>
+        <v>1366</v>
       </c>
       <c r="L578" s="1"/>
     </row>

--- a/Liquid+ Project/Sélection des startups/processus de sélection des startups GAIA.xlsx
+++ b/Liquid+ Project/Sélection des startups/processus de sélection des startups GAIA.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="1355">
   <si>
     <t>décision de Liquid+</t>
   </si>
@@ -4024,13 +4024,76 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/xavier-silvani-a6058985/</t>
+  </si>
+  <si>
+    <t>mail envoyé ?</t>
+  </si>
+  <si>
+    <t>linkedin envoyé ?</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/k%C3%A9vin-jaboviste-9b5219217/</t>
+  </si>
+  <si>
+    <t>marc barsoum, julien maruotti</t>
+  </si>
+  <si>
+    <t>Batti</t>
+  </si>
+  <si>
+    <t>contact@anodine.fr</t>
+  </si>
+  <si>
+    <t>Damien Leguerrier, Richard Barré, Baptiste Dautreppe</t>
+  </si>
+  <si>
+    <t>kader.zaidat@krystalix.com</t>
+  </si>
+  <si>
+    <t>Kader ZAIDAT</t>
+  </si>
+  <si>
+    <t>contact@saxol.eu</t>
+  </si>
+  <si>
+    <t>Philippe Bordeau, Laurianne Le Pennec, Victor Juarez Perez</t>
+  </si>
+  <si>
+    <t>Emile Roussel, Lise Clément-Demange</t>
+  </si>
+  <si>
+    <t>contact@react-therapeutics.com </t>
+  </si>
+  <si>
+    <t>guillaume franque</t>
+  </si>
+  <si>
+    <t>info@nveil.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@theyeq.com </t>
+  </si>
+  <si>
+    <t>Copernic</t>
+  </si>
+  <si>
+    <t>Nicolas Roy, Gautier Guignard</t>
+  </si>
+  <si>
+    <t>Claude Roy, et probablement un autre</t>
+  </si>
+  <si>
+    <t>islam.eb@hotmail.fr</t>
+  </si>
+  <si>
+    <t>Islam El Boudi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4058,6 +4121,24 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF242424"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1C1835"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -4092,7 +4173,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
@@ -4100,12 +4181,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -4119,6 +4194,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -4417,2034 +4495,2164 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N1001"/>
+  <dimension ref="A1:P1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.90625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="25.90625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="28.36328125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="22.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="82.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.7265625" style="7"/>
+    <col min="3" max="3" width="5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.90625" style="1" customWidth="1"/>
+    <col min="6" max="8" width="25.90625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="28.36328125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="82.7265625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>16</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A5" t="s">
+    <row r="5" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>27</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>16</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" t="s">
+      <c r="F6" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>35</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>27</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>16</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A7" t="s">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>37</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>27</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>16</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A8" t="s">
+    <row r="8" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" t="s">
         <v>40</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>16</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>43</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>44</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>27</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>16</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>46</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>47</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>27</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>16</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" spans="1:16" ht="18.75" customHeight="1">
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>49</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>27</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>16</v>
       </c>
-      <c r="M11" t="s">
+      <c r="O11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18.75" customHeight="1">
-      <c r="B12" t="s">
+    <row r="12" spans="1:16" ht="18.75" customHeight="1">
+      <c r="D12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>51</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
         <v>52</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>27</v>
       </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
         <v>16</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A14" t="s">
+    <row r="14" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" t="s">
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" t="s">
         <v>58</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>59</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>27</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>16</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" spans="1:16" ht="18.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" t="s">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" t="s">
         <v>62</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>63</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>27</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>16</v>
       </c>
-      <c r="M15" t="s">
+      <c r="O15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="18.75" customHeight="1">
-      <c r="B16" t="s">
+    <row r="16" spans="1:16" ht="18.75" customHeight="1">
+      <c r="D16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" t="s">
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" t="s">
         <v>66</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>67</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>27</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
         <v>16</v>
       </c>
-      <c r="M16" t="s">
+      <c r="O16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B17" t="s">
+    <row r="17" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>69</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>27</v>
       </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
         <v>16</v>
       </c>
-      <c r="M17" t="s">
+      <c r="O17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B18" t="s">
+    <row r="18" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>71</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>72</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>27</v>
       </c>
-      <c r="L18" t="s">
+      <c r="N18" t="s">
         <v>16</v>
       </c>
-      <c r="M18" t="s">
+      <c r="O18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B19" t="s">
+    <row r="19" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>74</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" t="s">
         <v>44</v>
       </c>
-      <c r="I19" t="s">
+      <c r="K19" t="s">
         <v>75</v>
       </c>
-      <c r="L19" t="s">
+      <c r="N19" t="s">
         <v>16</v>
       </c>
-      <c r="M19" t="s">
+      <c r="O19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>1289</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="1" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>77</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>75</v>
       </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
         <v>16</v>
       </c>
-      <c r="M20" t="s">
+      <c r="O20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>1291</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="6" t="s">
         <v>1292</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>14</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>79</v>
       </c>
-      <c r="L21" t="s">
+      <c r="N21" t="s">
         <v>16</v>
       </c>
-      <c r="M21" t="s">
+      <c r="O21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B22" t="s">
+    <row r="22" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>81</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>79</v>
       </c>
-      <c r="L22" t="s">
+      <c r="N22" t="s">
         <v>16</v>
       </c>
-      <c r="M22" t="s">
+      <c r="O22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:15" ht="18.75" customHeight="1">
+      <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>1295</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="1" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>83</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>79</v>
       </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>16</v>
       </c>
-      <c r="M23" t="s">
+      <c r="O23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B24" s="1" t="s">
+    <row r="24" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>83</v>
       </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
         <v>79</v>
       </c>
-      <c r="L24" t="s">
+      <c r="N24" t="s">
         <v>16</v>
       </c>
-      <c r="M24" t="s">
+      <c r="O24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>1296</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="6" t="s">
         <v>1297</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>41</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>79</v>
       </c>
-      <c r="L25" t="s">
+      <c r="N25" t="s">
         <v>16</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B26" s="1" t="s">
+    <row r="26" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>1298</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="H26" s="5" t="s">
         <v>1301</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="I26" s="6" t="s">
         <v>1299</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>86</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>79</v>
       </c>
-      <c r="L26" t="s">
+      <c r="N26" t="s">
         <v>16</v>
       </c>
-      <c r="M26" t="s">
+      <c r="O26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B27" t="s">
+    <row r="27" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>1302</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
         <v>88</v>
       </c>
-      <c r="I27" t="s">
+      <c r="K27" t="s">
         <v>79</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>16</v>
       </c>
-      <c r="M27" t="s">
+      <c r="O27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B28" t="s">
+    <row r="28" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>1303</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>90</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>79</v>
       </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>16</v>
       </c>
-      <c r="M28" t="s">
+      <c r="O28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B29" t="s">
+    <row r="29" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>1304</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>92</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>79</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>16</v>
       </c>
-      <c r="M29" t="s">
+      <c r="O29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B30" t="s">
+    <row r="30" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A30" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>1305</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J30" t="s">
         <v>94</v>
       </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
         <v>79</v>
       </c>
-      <c r="L30" t="s">
+      <c r="N30" t="s">
         <v>16</v>
       </c>
-      <c r="M30" t="s">
+      <c r="O30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D31" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="F31" s="7" t="s">
         <v>1307</v>
       </c>
-      <c r="H31" t="s">
+      <c r="J31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" t="s">
+      <c r="K31" t="s">
         <v>79</v>
       </c>
-      <c r="L31" t="s">
+      <c r="N31" t="s">
         <v>16</v>
       </c>
-      <c r="M31" t="s">
+      <c r="O31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18.75" customHeight="1">
-      <c r="B32" t="s">
+    <row r="32" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="E32" s="5" t="s">
         <v>1308</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>1309</v>
       </c>
-      <c r="H32" t="s">
+      <c r="J32" t="s">
         <v>96</v>
       </c>
-      <c r="I32" t="s">
+      <c r="K32" t="s">
         <v>79</v>
       </c>
-      <c r="L32" t="s">
+      <c r="N32" t="s">
         <v>16</v>
       </c>
-      <c r="M32" t="s">
+      <c r="O32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B33" s="1" t="s">
+    <row r="33" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D33" s="3" t="s">
         <v>1311</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>1310</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>97</v>
       </c>
-      <c r="I33" t="s">
+      <c r="K33" t="s">
         <v>79</v>
       </c>
-      <c r="L33" t="s">
+      <c r="N33" t="s">
         <v>16</v>
       </c>
-      <c r="M33" t="s">
+      <c r="O33" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B34" t="s">
+    <row r="34" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>99</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>79</v>
       </c>
-      <c r="L34" t="s">
+      <c r="N34" t="s">
         <v>16</v>
       </c>
-      <c r="M34" t="s">
+      <c r="O34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B35" t="s">
+    <row r="35" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D35" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>1312</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>101</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>79</v>
       </c>
-      <c r="L35" t="s">
+      <c r="N35" t="s">
         <v>16</v>
       </c>
-      <c r="M35" t="s">
+      <c r="O35" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B36" t="s">
+    <row r="36" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D36" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="E36" s="5" t="s">
         <v>1315</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="F36" s="7" t="s">
         <v>1314</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
         <v>103</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>104</v>
       </c>
-      <c r="L36" t="s">
+      <c r="N36" t="s">
         <v>16</v>
       </c>
-      <c r="M36" t="s">
+      <c r="O36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B37" t="s">
+    <row r="37" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D37" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="E37" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="F37" s="7" t="s">
         <v>1316</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>106</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>104</v>
       </c>
-      <c r="L37" t="s">
+      <c r="N37" t="s">
         <v>16</v>
       </c>
-      <c r="M37" t="s">
+      <c r="O37" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B38" t="s">
+    <row r="38" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D38" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="F38" s="7" t="s">
         <v>1318</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>108</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>104</v>
       </c>
-      <c r="L38" t="s">
+      <c r="N38" t="s">
         <v>16</v>
       </c>
-      <c r="M38" t="s">
+      <c r="O38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B39" t="s">
+    <row r="39" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D39" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="E39" s="6" t="s">
         <v>1319</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="G39" s="5" t="s">
         <v>1320</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>110</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>104</v>
       </c>
-      <c r="L39" t="s">
+      <c r="N39" t="s">
         <v>16</v>
       </c>
-      <c r="M39" t="s">
+      <c r="O39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B40" t="s">
+    <row r="40" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A40" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="E40" s="5" t="s">
         <v>1321</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="F40" s="7" t="s">
         <v>1322</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="G40" s="5" t="s">
         <v>1323</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>112</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>113</v>
       </c>
-      <c r="L40" t="s">
+      <c r="N40" t="s">
         <v>114</v>
       </c>
-      <c r="M40" t="s">
+      <c r="O40" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B41" t="s">
+    <row r="41" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D41" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>117</v>
       </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>118</v>
       </c>
-      <c r="L41" t="s">
+      <c r="N41" t="s">
         <v>114</v>
       </c>
-      <c r="M41" t="s">
+      <c r="O41" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B42" t="s">
+    <row r="42" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A42" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="E42" s="5" t="s">
         <v>1324</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="F42" s="7" t="s">
         <v>1326</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="G42" s="5" t="s">
         <v>1325</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
         <v>120</v>
       </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>118</v>
       </c>
-      <c r="L42" t="s">
+      <c r="N42" t="s">
         <v>114</v>
       </c>
-      <c r="M42" t="s">
+      <c r="O42" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B43" t="s">
+    <row r="43" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D43" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="F43" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>1327</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" t="s">
         <v>123</v>
       </c>
-      <c r="L43" t="s">
+      <c r="N43" t="s">
         <v>114</v>
       </c>
-      <c r="M43" t="s">
+      <c r="O43" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="1:15" ht="18.75" customHeight="1">
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>1330</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="E44" s="5" t="s">
         <v>1328</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="F44" s="7" t="s">
         <v>1329</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>1331</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>124</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>123</v>
       </c>
-      <c r="L44" t="s">
+      <c r="N44" t="s">
         <v>114</v>
       </c>
-      <c r="M44" t="s">
+      <c r="O44" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B45" t="s">
+    <row r="45" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D45" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="F45" s="7" t="s">
         <v>1332</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="G45" s="5" t="s">
         <v>1333</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>123</v>
       </c>
-      <c r="L45" t="s">
+      <c r="N45" t="s">
         <v>114</v>
       </c>
-      <c r="M45" t="s">
+      <c r="O45" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="47" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="48" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="49" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="50" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="51" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="52" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B52" t="s">
+    <row r="46" spans="1:15" ht="18.75" customHeight="1"/>
+    <row r="47" spans="1:15" ht="18.75" customHeight="1"/>
+    <row r="48" spans="1:15" ht="18.75" customHeight="1"/>
+    <row r="49" spans="1:15" ht="18.75" customHeight="1"/>
+    <row r="50" spans="1:15" ht="18.75" customHeight="1"/>
+    <row r="51" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D51" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A52" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H52" t="s">
+      <c r="E52" s="11" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>1340</v>
+      </c>
+      <c r="J52" t="s">
         <v>128</v>
       </c>
-      <c r="I52" t="s">
+      <c r="K52" t="s">
         <v>129</v>
       </c>
-      <c r="L52" t="s">
+      <c r="N52" t="s">
         <v>130</v>
       </c>
-      <c r="M52" t="s">
+      <c r="O52" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B53" t="s">
+    <row r="53" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A53" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H53" t="s">
+      <c r="E53" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J53" t="s">
         <v>133</v>
       </c>
-      <c r="I53" t="s">
+      <c r="K53" t="s">
         <v>134</v>
       </c>
-      <c r="L53" t="s">
+      <c r="N53" t="s">
         <v>130</v>
       </c>
-      <c r="M53" t="s">
+      <c r="O53" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="54" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B54" t="s">
+    <row r="54" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A54" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H54" t="s">
+      <c r="E54" s="5" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J54" t="s">
         <v>136</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
         <v>137</v>
       </c>
-      <c r="L54" t="s">
+      <c r="N54" t="s">
         <v>130</v>
       </c>
-      <c r="M54" t="s">
+      <c r="O54" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B55" t="s">
+    <row r="55" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A55" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H55" t="s">
+      <c r="E55" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J55" t="s">
         <v>139</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>140</v>
       </c>
-      <c r="L55" t="s">
+      <c r="N55" t="s">
         <v>130</v>
       </c>
-      <c r="M55" t="s">
+      <c r="O55" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B56" t="s">
+    <row r="56" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A56" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H56" t="s">
+      <c r="E56" s="12" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J56" t="s">
         <v>142</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>143</v>
       </c>
-      <c r="L56" t="s">
+      <c r="N56" t="s">
         <v>130</v>
       </c>
-      <c r="M56" t="s">
+      <c r="O56" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B57" t="s">
+    <row r="57" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A57" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H57" t="s">
+      <c r="E57" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J57" t="s">
         <v>145</v>
       </c>
-      <c r="I57" t="s">
+      <c r="K57" t="s">
         <v>143</v>
       </c>
-      <c r="L57" t="s">
+      <c r="N57" t="s">
         <v>130</v>
       </c>
-      <c r="M57" t="s">
+      <c r="O57" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B58" t="s">
+    <row r="58" spans="1:15" ht="18.75" customHeight="1">
+      <c r="A58" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H58" t="s">
+      <c r="E58" s="13" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J58" t="s">
         <v>147</v>
       </c>
-      <c r="I58" t="s">
+      <c r="K58" t="s">
         <v>143</v>
       </c>
-      <c r="L58" t="s">
+      <c r="N58" t="s">
         <v>130</v>
       </c>
-      <c r="M58" t="s">
+      <c r="O58" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B59" t="s">
+    <row r="59" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D59" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>149</v>
       </c>
-      <c r="I59" t="s">
+      <c r="K59" t="s">
         <v>143</v>
       </c>
-      <c r="L59" t="s">
+      <c r="N59" t="s">
         <v>130</v>
       </c>
-      <c r="M59" t="s">
+      <c r="O59" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B60" t="s">
+    <row r="60" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D60" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H60" t="s">
+      <c r="J60" t="s">
         <v>151</v>
       </c>
-      <c r="I60" t="s">
+      <c r="K60" t="s">
         <v>152</v>
       </c>
-      <c r="L60" t="s">
+      <c r="N60" t="s">
         <v>130</v>
       </c>
-      <c r="M60" t="s">
+      <c r="O60" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B61" t="s">
+    <row r="61" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D61" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H61" t="s">
+      <c r="J61" t="s">
         <v>154</v>
       </c>
-      <c r="I61" t="s">
+      <c r="K61" t="s">
         <v>152</v>
       </c>
-      <c r="L61" t="s">
+      <c r="N61" t="s">
         <v>130</v>
       </c>
-      <c r="M61" t="s">
+      <c r="O61" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B62" t="s">
+    <row r="62" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D62" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>156</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>152</v>
       </c>
-      <c r="L62" t="s">
+      <c r="N62" t="s">
         <v>130</v>
       </c>
-      <c r="M62" t="s">
+      <c r="O62" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B63" t="s">
+    <row r="63" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D63" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H63" t="s">
+      <c r="J63" t="s">
         <v>158</v>
       </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>152</v>
       </c>
-      <c r="L63" t="s">
+      <c r="N63" t="s">
         <v>130</v>
       </c>
-      <c r="M63" t="s">
+      <c r="O63" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B64" t="s">
+    <row r="64" spans="1:15" ht="18.75" customHeight="1">
+      <c r="D64" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H64" t="s">
+      <c r="J64" t="s">
         <v>160</v>
       </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>152</v>
       </c>
-      <c r="L64" t="s">
+      <c r="N64" t="s">
         <v>130</v>
       </c>
-      <c r="M64" t="s">
+      <c r="O64" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B65" t="s">
+    <row r="65" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D65" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H65" t="s">
+      <c r="J65" t="s">
         <v>162</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>152</v>
       </c>
-      <c r="L65" t="s">
+      <c r="N65" t="s">
         <v>130</v>
       </c>
-      <c r="M65" t="s">
+      <c r="O65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B66" t="s">
+    <row r="66" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D66" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H66" t="s">
+      <c r="J66" t="s">
         <v>164</v>
       </c>
-      <c r="I66" t="s">
+      <c r="K66" t="s">
         <v>152</v>
       </c>
-      <c r="L66" t="s">
+      <c r="N66" t="s">
         <v>130</v>
       </c>
-      <c r="M66" t="s">
+      <c r="O66" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B67" t="s">
+    <row r="67" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D67" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H67" t="s">
+      <c r="J67" t="s">
         <v>166</v>
       </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>152</v>
       </c>
-      <c r="L67" t="s">
+      <c r="N67" t="s">
         <v>130</v>
       </c>
-      <c r="M67" t="s">
+      <c r="O67" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B68" t="s">
+    <row r="68" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D68" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
         <v>168</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>152</v>
       </c>
-      <c r="L68" t="s">
+      <c r="N68" t="s">
         <v>130</v>
       </c>
-      <c r="M68" t="s">
+      <c r="O68" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B69" t="s">
+    <row r="69" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D69" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H69" t="s">
+      <c r="J69" t="s">
         <v>170</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
         <v>152</v>
       </c>
-      <c r="L69" t="s">
+      <c r="N69" t="s">
         <v>130</v>
       </c>
-      <c r="M69" t="s">
+      <c r="O69" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B70" t="s">
+    <row r="70" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D70" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="H70" t="s">
+      <c r="J70" t="s">
         <v>172</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>152</v>
       </c>
-      <c r="L70" t="s">
+      <c r="N70" t="s">
         <v>130</v>
       </c>
-      <c r="M70" t="s">
+      <c r="O70" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="71" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B71" t="s">
+    <row r="71" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D71" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H71" t="s">
+      <c r="J71" t="s">
         <v>174</v>
       </c>
-      <c r="I71" t="s">
+      <c r="K71" t="s">
         <v>152</v>
       </c>
-      <c r="L71" t="s">
+      <c r="N71" t="s">
         <v>130</v>
       </c>
-      <c r="M71" t="s">
+      <c r="O71" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B72" t="s">
+    <row r="72" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D72" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H72" t="s">
+      <c r="J72" t="s">
         <v>176</v>
       </c>
-      <c r="I72" t="s">
+      <c r="K72" t="s">
         <v>152</v>
       </c>
-      <c r="L72" t="s">
+      <c r="N72" t="s">
         <v>130</v>
       </c>
-      <c r="M72" t="s">
+      <c r="O72" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="73" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B73" t="s">
+    <row r="73" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D73" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H73" t="s">
+      <c r="J73" t="s">
         <v>178</v>
       </c>
-      <c r="I73" t="s">
+      <c r="K73" t="s">
         <v>152</v>
       </c>
-      <c r="L73" t="s">
+      <c r="N73" t="s">
         <v>130</v>
       </c>
-      <c r="M73" t="s">
+      <c r="O73" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="74" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B74" t="s">
+    <row r="74" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D74" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H74" t="s">
+      <c r="J74" t="s">
         <v>180</v>
       </c>
-      <c r="I74" t="s">
+      <c r="K74" t="s">
         <v>152</v>
       </c>
-      <c r="L74" t="s">
+      <c r="N74" t="s">
         <v>130</v>
       </c>
-      <c r="M74" t="s">
+      <c r="O74" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B75" t="s">
+    <row r="75" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D75" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H75" t="s">
+      <c r="J75" t="s">
         <v>182</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>152</v>
       </c>
-      <c r="L75" t="s">
+      <c r="N75" t="s">
         <v>130</v>
       </c>
-      <c r="M75" t="s">
+      <c r="O75" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="76" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B76" t="s">
+    <row r="76" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D76" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H76" t="s">
+      <c r="J76" t="s">
         <v>184</v>
       </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>152</v>
       </c>
-      <c r="L76" t="s">
+      <c r="N76" t="s">
         <v>130</v>
       </c>
-      <c r="M76" t="s">
+      <c r="O76" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B77" t="s">
+    <row r="77" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D77" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H77" t="s">
+      <c r="J77" t="s">
         <v>186</v>
       </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>152</v>
       </c>
-      <c r="L77" t="s">
+      <c r="N77" t="s">
         <v>130</v>
       </c>
-      <c r="M77" t="s">
+      <c r="O77" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B78" t="s">
+    <row r="78" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D78" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
         <v>188</v>
       </c>
-      <c r="I78" t="s">
+      <c r="K78" t="s">
         <v>152</v>
       </c>
-      <c r="L78" t="s">
+      <c r="N78" t="s">
         <v>130</v>
       </c>
-      <c r="M78" t="s">
+      <c r="O78" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="79" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B79" t="s">
+    <row r="79" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D79" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H79" t="s">
+      <c r="J79" t="s">
         <v>190</v>
       </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>152</v>
       </c>
-      <c r="L79" t="s">
+      <c r="N79" t="s">
         <v>130</v>
       </c>
-      <c r="M79" t="s">
+      <c r="O79" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="80" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B80" t="s">
+    <row r="80" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D80" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C80" t="s">
+      <c r="E80" t="s">
         <v>192</v>
       </c>
-      <c r="G80" t="s">
+      <c r="I80" t="s">
         <v>193</v>
       </c>
-      <c r="H80" t="s">
+      <c r="J80" t="s">
         <v>194</v>
       </c>
-      <c r="I80" t="s">
+      <c r="K80" t="s">
         <v>195</v>
       </c>
-      <c r="L80" t="s">
+      <c r="N80" t="s">
         <v>196</v>
       </c>
-      <c r="M80" t="s">
+      <c r="O80" t="s">
         <v>197</v>
       </c>
-      <c r="N80" t="s">
+      <c r="P80" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B81" t="s">
+    <row r="81" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D81" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C81" t="s">
+      <c r="E81" t="s">
         <v>200</v>
       </c>
-      <c r="G81" t="s">
+      <c r="I81" t="s">
         <v>201</v>
       </c>
-      <c r="H81" t="s">
+      <c r="J81" t="s">
         <v>202</v>
       </c>
-      <c r="I81" t="s">
+      <c r="K81" t="s">
         <v>195</v>
       </c>
-      <c r="L81" t="s">
+      <c r="N81" t="s">
         <v>196</v>
       </c>
-      <c r="M81" t="s">
+      <c r="O81" t="s">
         <v>197</v>
       </c>
-      <c r="N81" t="s">
+      <c r="P81" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B82" t="s">
+    <row r="82" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D82" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C82" t="s">
+      <c r="E82" t="s">
         <v>205</v>
       </c>
-      <c r="G82" t="s">
+      <c r="I82" t="s">
         <v>206</v>
       </c>
-      <c r="H82" t="s">
+      <c r="J82" t="s">
         <v>207</v>
       </c>
-      <c r="I82" t="s">
+      <c r="K82" t="s">
         <v>195</v>
       </c>
-      <c r="L82" t="s">
+      <c r="N82" t="s">
         <v>196</v>
       </c>
-      <c r="M82" t="s">
+      <c r="O82" t="s">
         <v>197</v>
       </c>
-      <c r="N82" t="s">
+      <c r="P82" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="83" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B83" t="s">
+    <row r="83" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D83" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" t="s">
         <v>209</v>
       </c>
-      <c r="G83" t="s">
+      <c r="I83" t="s">
         <v>210</v>
       </c>
-      <c r="H83" t="s">
+      <c r="J83" t="s">
         <v>211</v>
       </c>
-      <c r="I83" t="s">
+      <c r="K83" t="s">
         <v>195</v>
       </c>
-      <c r="L83" t="s">
+      <c r="N83" t="s">
         <v>196</v>
       </c>
-      <c r="M83" t="s">
+      <c r="O83" t="s">
         <v>197</v>
       </c>
-      <c r="N83" t="s">
+      <c r="P83" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="84" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B84" t="s">
+    <row r="84" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D84" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
         <v>214</v>
       </c>
-      <c r="G84" t="s">
+      <c r="I84" t="s">
         <v>215</v>
       </c>
-      <c r="H84" t="s">
+      <c r="J84" t="s">
         <v>216</v>
       </c>
-      <c r="I84" t="s">
+      <c r="K84" t="s">
         <v>195</v>
       </c>
-      <c r="L84" t="s">
+      <c r="N84" t="s">
         <v>196</v>
       </c>
-      <c r="M84" t="s">
+      <c r="O84" t="s">
         <v>197</v>
       </c>
-      <c r="N84" t="s">
+      <c r="P84" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="85" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B85" t="s">
+    <row r="85" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D85" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E85" t="s">
         <v>218</v>
       </c>
-      <c r="G85" t="s">
+      <c r="I85" t="s">
         <v>219</v>
       </c>
-      <c r="H85" t="s">
+      <c r="J85" t="s">
         <v>220</v>
       </c>
-      <c r="I85" t="s">
+      <c r="K85" t="s">
         <v>195</v>
       </c>
-      <c r="L85" t="s">
+      <c r="N85" t="s">
         <v>196</v>
       </c>
-      <c r="M85" t="s">
+      <c r="O85" t="s">
         <v>197</v>
       </c>
-      <c r="N85" t="s">
+      <c r="P85" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="86" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B86" t="s">
+    <row r="86" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D86" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C86" t="s">
+      <c r="E86" t="s">
         <v>222</v>
       </c>
-      <c r="G86" t="s">
+      <c r="I86" t="s">
         <v>223</v>
       </c>
-      <c r="H86" t="s">
+      <c r="J86" t="s">
         <v>224</v>
       </c>
-      <c r="I86" t="s">
+      <c r="K86" t="s">
         <v>195</v>
       </c>
-      <c r="L86" t="s">
+      <c r="N86" t="s">
         <v>196</v>
       </c>
-      <c r="M86" t="s">
+      <c r="O86" t="s">
         <v>197</v>
       </c>
-      <c r="N86" t="s">
+      <c r="P86" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="87" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B87" t="s">
+    <row r="87" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D87" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
         <v>226</v>
       </c>
-      <c r="G87" t="s">
+      <c r="I87" t="s">
         <v>227</v>
       </c>
-      <c r="H87" t="s">
+      <c r="J87" t="s">
         <v>228</v>
       </c>
-      <c r="I87" t="s">
+      <c r="K87" t="s">
         <v>195</v>
       </c>
-      <c r="L87" t="s">
+      <c r="N87" t="s">
         <v>196</v>
       </c>
-      <c r="M87" t="s">
+      <c r="O87" t="s">
         <v>197</v>
       </c>
-      <c r="N87" t="s">
+      <c r="P87" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="88" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B88" t="s">
+    <row r="88" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D88" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C88" t="s">
+      <c r="E88" t="s">
         <v>231</v>
       </c>
-      <c r="G88" t="s">
+      <c r="I88" t="s">
         <v>232</v>
       </c>
-      <c r="H88" t="s">
+      <c r="J88" t="s">
         <v>233</v>
       </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
         <v>234</v>
       </c>
-      <c r="L88" t="s">
+      <c r="N88" t="s">
         <v>235</v>
       </c>
-      <c r="M88" t="s">
+      <c r="O88" t="s">
         <v>236</v>
       </c>
-      <c r="N88" t="s">
+      <c r="P88" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="89" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B89" t="s">
+    <row r="89" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D89" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C89" t="s">
+      <c r="E89" t="s">
         <v>239</v>
       </c>
-      <c r="G89" t="s">
+      <c r="I89" t="s">
         <v>240</v>
       </c>
-      <c r="H89" t="s">
+      <c r="J89" t="s">
         <v>241</v>
       </c>
-      <c r="I89" t="s">
+      <c r="K89" t="s">
         <v>234</v>
       </c>
-      <c r="L89" t="s">
+      <c r="N89" t="s">
         <v>235</v>
       </c>
-      <c r="M89" t="s">
+      <c r="O89" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="90" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B90" t="s">
+    <row r="90" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D90" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G90" t="s">
+      <c r="I90" t="s">
         <v>243</v>
       </c>
-      <c r="H90" t="s">
+      <c r="J90" t="s">
         <v>244</v>
       </c>
-      <c r="I90" t="s">
+      <c r="K90" t="s">
         <v>234</v>
       </c>
-      <c r="L90" t="s">
+      <c r="N90" t="s">
         <v>235</v>
       </c>
-      <c r="M90" t="s">
+      <c r="O90" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B91" t="s">
+    <row r="91" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D91" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" t="s">
         <v>246</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
         <v>247</v>
       </c>
-      <c r="H91" t="s">
+      <c r="J91" t="s">
         <v>248</v>
       </c>
-      <c r="I91" t="s">
+      <c r="K91" t="s">
         <v>234</v>
       </c>
-      <c r="L91" t="s">
+      <c r="N91" t="s">
         <v>235</v>
       </c>
-      <c r="M91" t="s">
+      <c r="O91" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B92" t="s">
+    <row r="92" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D92" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H92" t="s">
+      <c r="J92" t="s">
         <v>250</v>
       </c>
-      <c r="I92" t="s">
+      <c r="K92" t="s">
         <v>251</v>
       </c>
-      <c r="L92" t="s">
+      <c r="N92" t="s">
         <v>252</v>
       </c>
-      <c r="M92" t="s">
+      <c r="O92" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="93" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B93" t="s">
+    <row r="93" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D93" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="H93" t="s">
+      <c r="J93" t="s">
         <v>255</v>
       </c>
-      <c r="I93" t="s">
+      <c r="K93" t="s">
         <v>251</v>
       </c>
-      <c r="L93" t="s">
+      <c r="N93" t="s">
         <v>252</v>
       </c>
-      <c r="M93" t="s">
+      <c r="O93" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="94" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B94" t="s">
+    <row r="94" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D94" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H94" t="s">
+      <c r="J94" t="s">
         <v>257</v>
       </c>
-      <c r="I94" t="s">
+      <c r="K94" t="s">
         <v>251</v>
       </c>
-      <c r="L94" t="s">
+      <c r="N94" t="s">
         <v>252</v>
       </c>
-      <c r="M94" t="s">
+      <c r="O94" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="95" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B95" t="s">
+    <row r="95" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D95" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H95" t="s">
+      <c r="J95" t="s">
         <v>259</v>
       </c>
-      <c r="I95" t="s">
+      <c r="K95" t="s">
         <v>251</v>
       </c>
-      <c r="L95" t="s">
+      <c r="N95" t="s">
         <v>252</v>
       </c>
-      <c r="M95" t="s">
+      <c r="O95" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="96" spans="2:14" ht="18.75" customHeight="1">
-      <c r="B96" t="s">
+    <row r="96" spans="4:16" ht="18.75" customHeight="1">
+      <c r="D96" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="H96" t="s">
+      <c r="J96" t="s">
         <v>261</v>
       </c>
-      <c r="I96" t="s">
+      <c r="K96" t="s">
         <v>251</v>
       </c>
-      <c r="L96" t="s">
+      <c r="N96" t="s">
         <v>252</v>
       </c>
-      <c r="M96" t="s">
+      <c r="O96" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="97" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B97" t="s">
+    <row r="97" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D97" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="H97" t="s">
+      <c r="J97" t="s">
         <v>263</v>
       </c>
-      <c r="I97" t="s">
+      <c r="K97" t="s">
         <v>251</v>
       </c>
-      <c r="L97" t="s">
+      <c r="N97" t="s">
         <v>252</v>
       </c>
-      <c r="M97" t="s">
+      <c r="O97" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="98" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B98" t="s">
+    <row r="98" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D98" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H98" t="s">
+      <c r="J98" t="s">
         <v>265</v>
       </c>
-      <c r="I98" t="s">
+      <c r="K98" t="s">
         <v>251</v>
       </c>
-      <c r="L98" t="s">
+      <c r="N98" t="s">
         <v>252</v>
       </c>
-      <c r="M98" t="s">
+      <c r="O98" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="99" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B99" t="s">
+    <row r="99" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D99" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H99" t="s">
+      <c r="J99" t="s">
         <v>267</v>
       </c>
-      <c r="I99" t="s">
+      <c r="K99" t="s">
         <v>251</v>
       </c>
-      <c r="L99" t="s">
+      <c r="N99" t="s">
         <v>252</v>
       </c>
-      <c r="M99" t="s">
+      <c r="O99" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B100" t="s">
+    <row r="100" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D100" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="H100" t="s">
+      <c r="J100" t="s">
         <v>269</v>
       </c>
-      <c r="I100" t="s">
+      <c r="K100" t="s">
         <v>251</v>
       </c>
-      <c r="L100" t="s">
+      <c r="N100" t="s">
         <v>252</v>
       </c>
-      <c r="M100" t="s">
+      <c r="O100" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="101" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B101" t="s">
+    <row r="101" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D101" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="H101" t="s">
+      <c r="J101" t="s">
         <v>271</v>
       </c>
-      <c r="I101" t="s">
+      <c r="K101" t="s">
         <v>251</v>
       </c>
-      <c r="L101" t="s">
+      <c r="N101" t="s">
         <v>252</v>
       </c>
-      <c r="M101" t="s">
+      <c r="O101" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="103" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="104" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="105" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="106" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="107" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="108" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="109" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="110" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="111" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="112" spans="2:13" ht="18.75" customHeight="1"/>
+    <row r="102" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="103" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="104" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="105" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="106" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="107" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="108" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="109" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="110" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="111" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="112" spans="4:15" ht="18.75" customHeight="1"/>
     <row r="113" ht="18.75" customHeight="1"/>
     <row r="114" ht="18.75" customHeight="1"/>
     <row r="115" ht="18.75" customHeight="1"/>
@@ -6829,1140 +7037,1140 @@
     <row r="494" ht="18.75" customHeight="1"/>
     <row r="495" ht="18.75" customHeight="1"/>
     <row r="496" ht="18.75" customHeight="1"/>
-    <row r="497" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="498" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="499" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="500" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B500" t="s">
+    <row r="497" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="498" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="499" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="500" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D500" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="H500" t="s">
+      <c r="J500" t="s">
         <v>273</v>
       </c>
-      <c r="M500" t="s">
+      <c r="O500" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="501" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B501" t="s">
+    <row r="501" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D501" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="H501" t="s">
+      <c r="J501" t="s">
         <v>276</v>
       </c>
-      <c r="M501" t="s">
+      <c r="O501" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="502" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B502" t="s">
+    <row r="502" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D502" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H502" t="s">
+      <c r="J502" t="s">
         <v>278</v>
       </c>
-      <c r="M502" t="s">
+      <c r="O502" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="503" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B503" t="s">
+    <row r="503" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D503" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="H503" t="s">
+      <c r="J503" t="s">
         <v>280</v>
       </c>
-      <c r="M503" t="s">
+      <c r="O503" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="504" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B504" t="s">
+    <row r="504" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D504" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="H504" t="s">
+      <c r="J504" t="s">
         <v>282</v>
       </c>
-      <c r="M504" t="s">
+      <c r="O504" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="505" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B505" t="s">
+    <row r="505" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D505" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="H505" t="s">
+      <c r="J505" t="s">
         <v>284</v>
       </c>
-      <c r="M505" t="s">
+      <c r="O505" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="506" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B506" t="s">
+    <row r="506" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D506" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H506" t="s">
+      <c r="J506" t="s">
         <v>286</v>
       </c>
-      <c r="M506" t="s">
+      <c r="O506" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="507" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B507" t="s">
+    <row r="507" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D507" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="H507" t="s">
+      <c r="J507" t="s">
         <v>288</v>
       </c>
-      <c r="M507" t="s">
+      <c r="O507" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="508" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B508" t="s">
+    <row r="508" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D508" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="H508" t="s">
+      <c r="J508" t="s">
         <v>290</v>
       </c>
-      <c r="M508" t="s">
+      <c r="O508" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="509" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B509" t="s">
+    <row r="509" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D509" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H509" t="s">
+      <c r="J509" t="s">
         <v>292</v>
       </c>
-      <c r="M509" t="s">
+      <c r="O509" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="510" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B510" t="s">
+    <row r="510" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D510" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H510" t="s">
+      <c r="J510" t="s">
         <v>294</v>
       </c>
-      <c r="I510" t="s">
+      <c r="K510" t="s">
         <v>295</v>
       </c>
-      <c r="M510" t="s">
+      <c r="O510" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="511" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B511" t="s">
+    <row r="511" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D511" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H511" t="s">
+      <c r="J511" t="s">
         <v>297</v>
       </c>
-      <c r="M511" t="s">
+      <c r="O511" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="512" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B512" t="s">
+    <row r="512" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D512" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="H512" t="s">
+      <c r="J512" t="s">
         <v>299</v>
       </c>
-      <c r="M512" t="s">
+      <c r="O512" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="513" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B513" t="s">
+    <row r="513" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D513" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H513" t="s">
+      <c r="J513" t="s">
         <v>301</v>
       </c>
-      <c r="M513" t="s">
+      <c r="O513" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="514" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B514" t="s">
+    <row r="514" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D514" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H514" t="s">
+      <c r="J514" t="s">
         <v>303</v>
       </c>
-      <c r="M514" t="s">
+      <c r="O514" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="515" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B515" t="s">
+    <row r="515" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D515" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H515" t="s">
+      <c r="J515" t="s">
         <v>305</v>
       </c>
-      <c r="M515" t="s">
+      <c r="O515" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="516" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B516" t="s">
+    <row r="516" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D516" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="H516" t="s">
+      <c r="J516" t="s">
         <v>307</v>
       </c>
-      <c r="M516" t="s">
+      <c r="O516" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="517" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B517" t="s">
+    <row r="517" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D517" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H517" t="s">
+      <c r="J517" t="s">
         <v>303</v>
       </c>
-      <c r="M517" t="s">
+      <c r="O517" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="518" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B518" t="s">
+    <row r="518" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D518" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H518" t="s">
+      <c r="J518" t="s">
         <v>310</v>
       </c>
-      <c r="M518" t="s">
+      <c r="O518" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="519" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B519" t="s">
+    <row r="519" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D519" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H519" t="s">
+      <c r="J519" t="s">
         <v>312</v>
       </c>
-      <c r="M519" t="s">
+      <c r="O519" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="520" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B520" t="s">
+    <row r="520" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D520" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H520" t="s">
+      <c r="J520" t="s">
         <v>314</v>
       </c>
-      <c r="M520" t="s">
+      <c r="O520" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="521" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B521" t="s">
+    <row r="521" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D521" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H521" t="s">
+      <c r="J521" t="s">
         <v>316</v>
       </c>
-      <c r="M521" t="s">
+      <c r="O521" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="522" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B522" t="s">
+    <row r="522" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D522" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H522" t="s">
+      <c r="J522" t="s">
         <v>318</v>
       </c>
-      <c r="I522" t="s">
+      <c r="K522" t="s">
         <v>319</v>
       </c>
-      <c r="M522" t="s">
+      <c r="O522" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="523" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B523" t="s">
+    <row r="523" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D523" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H523" t="s">
+      <c r="J523" t="s">
         <v>321</v>
       </c>
-      <c r="M523" t="s">
+      <c r="O523" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="524" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B524" t="s">
+    <row r="524" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D524" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H524" t="s">
+      <c r="J524" t="s">
         <v>323</v>
       </c>
-      <c r="M524" t="s">
+      <c r="O524" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="525" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B525" t="s">
+    <row r="525" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D525" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="H525" t="s">
+      <c r="J525" t="s">
         <v>325</v>
       </c>
-      <c r="I525" t="s">
+      <c r="K525" t="s">
         <v>295</v>
       </c>
-      <c r="M525" t="s">
+      <c r="O525" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="526" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B526" t="s">
+    <row r="526" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D526" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="H526" t="s">
+      <c r="J526" t="s">
         <v>327</v>
       </c>
-      <c r="I526" t="s">
+      <c r="K526" t="s">
         <v>328</v>
       </c>
-      <c r="M526" t="s">
+      <c r="O526" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="527" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B527" t="s">
+    <row r="527" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D527" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="H527" t="s">
+      <c r="J527" t="s">
         <v>330</v>
       </c>
-      <c r="M527" t="s">
+      <c r="O527" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="528" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B528" t="s">
+    <row r="528" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D528" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="H528" t="s">
+      <c r="J528" t="s">
         <v>332</v>
       </c>
-      <c r="M528" t="s">
+      <c r="O528" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="529" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B529" t="s">
+    <row r="529" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D529" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="H529" t="s">
+      <c r="J529" t="s">
         <v>334</v>
       </c>
-      <c r="I529" t="s">
+      <c r="K529" t="s">
         <v>335</v>
       </c>
-      <c r="L529" t="s">
+      <c r="N529" t="s">
         <v>336</v>
       </c>
-      <c r="M529" t="s">
+      <c r="O529" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="530" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B530" t="s">
+    <row r="530" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D530" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="H530" t="s">
+      <c r="J530" t="s">
         <v>339</v>
       </c>
-      <c r="I530" t="s">
+      <c r="K530" t="s">
         <v>340</v>
       </c>
-      <c r="L530" t="s">
+      <c r="N530" t="s">
         <v>341</v>
       </c>
-      <c r="M530" t="s">
+      <c r="O530" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="531" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B531" t="s">
+    <row r="531" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D531" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="H531" t="s">
+      <c r="J531" t="s">
         <v>343</v>
       </c>
-      <c r="I531" t="s">
+      <c r="K531" t="s">
         <v>344</v>
       </c>
-      <c r="L531" t="s">
+      <c r="N531" t="s">
         <v>345</v>
       </c>
-      <c r="M531" t="s">
+      <c r="O531" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="532" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B532" t="s">
+    <row r="532" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D532" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="H532" t="s">
+      <c r="J532" t="s">
         <v>347</v>
       </c>
-      <c r="L532" t="s">
+      <c r="N532" t="s">
         <v>348</v>
       </c>
-      <c r="M532" t="s">
+      <c r="O532" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="533" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B533" t="s">
+    <row r="533" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D533" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="H533" t="s">
+      <c r="J533" t="s">
         <v>347</v>
       </c>
-      <c r="L533" t="s">
+      <c r="N533" t="s">
         <v>348</v>
       </c>
-      <c r="M533" t="s">
+      <c r="O533" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="534" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B534" t="s">
+    <row r="534" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D534" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="H534" t="s">
+      <c r="J534" t="s">
         <v>347</v>
       </c>
-      <c r="L534" t="s">
+      <c r="N534" t="s">
         <v>351</v>
       </c>
-      <c r="M534" t="s">
+      <c r="O534" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="535" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B535" t="s">
+    <row r="535" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D535" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="H535" t="s">
+      <c r="J535" t="s">
         <v>347</v>
       </c>
-      <c r="L535" t="s">
+      <c r="N535" t="s">
         <v>348</v>
       </c>
-      <c r="M535" t="s">
+      <c r="O535" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="536" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B536" t="s">
+    <row r="536" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D536" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="H536" t="s">
+      <c r="J536" t="s">
         <v>347</v>
       </c>
-      <c r="L536" t="s">
+      <c r="N536" t="s">
         <v>348</v>
       </c>
-      <c r="M536" t="s">
+      <c r="O536" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="537" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B537" t="s">
+    <row r="537" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D537" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="H537" t="s">
+      <c r="J537" t="s">
         <v>347</v>
       </c>
-      <c r="L537" t="s">
+      <c r="N537" t="s">
         <v>355</v>
       </c>
-      <c r="M537" t="s">
+      <c r="O537" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="538" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B538" t="s">
+    <row r="538" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D538" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="H538" t="s">
+      <c r="J538" t="s">
         <v>347</v>
       </c>
-      <c r="L538" t="s">
+      <c r="N538" t="s">
         <v>348</v>
       </c>
-      <c r="M538" t="s">
+      <c r="O538" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="539" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B539" t="s">
+    <row r="539" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D539" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="H539" t="s">
+      <c r="J539" t="s">
         <v>347</v>
       </c>
-      <c r="L539" t="s">
+      <c r="N539" t="s">
         <v>348</v>
       </c>
-      <c r="M539" t="s">
+      <c r="O539" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="540" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B540" t="s">
+    <row r="540" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D540" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="H540" t="s">
+      <c r="J540" t="s">
         <v>347</v>
       </c>
-      <c r="L540" t="s">
+      <c r="N540" t="s">
         <v>348</v>
       </c>
-      <c r="M540" t="s">
+      <c r="O540" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="541" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B541" t="s">
+    <row r="541" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D541" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="H541" t="s">
+      <c r="J541" t="s">
         <v>360</v>
       </c>
-      <c r="L541" t="s">
+      <c r="N541" t="s">
         <v>361</v>
       </c>
-      <c r="M541" t="s">
+      <c r="O541" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="542" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B542" t="s">
+    <row r="542" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D542" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H542" t="s">
+      <c r="J542" t="s">
         <v>360</v>
       </c>
-      <c r="L542" t="s">
+      <c r="N542" t="s">
         <v>363</v>
       </c>
-      <c r="M542" t="s">
+      <c r="O542" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="543" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B543" t="s">
+    <row r="543" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D543" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="H543" t="s">
+      <c r="J543" t="s">
         <v>360</v>
       </c>
-      <c r="L543" t="s">
+      <c r="N543" t="s">
         <v>363</v>
       </c>
-      <c r="M543" t="s">
+      <c r="O543" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="544" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B544" t="s">
+    <row r="544" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D544" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="H544" t="s">
+      <c r="J544" t="s">
         <v>360</v>
       </c>
-      <c r="L544" t="s">
+      <c r="N544" t="s">
         <v>363</v>
       </c>
-      <c r="M544" t="s">
+      <c r="O544" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="545" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B545" t="s">
+    <row r="545" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D545" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H545" t="s">
+      <c r="J545" t="s">
         <v>367</v>
       </c>
-      <c r="L545" t="s">
+      <c r="N545" t="s">
         <v>368</v>
       </c>
-      <c r="M545" t="s">
+      <c r="O545" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="546" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B546" t="s">
+    <row r="546" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D546" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="H546" t="s">
+      <c r="J546" t="s">
         <v>367</v>
       </c>
-      <c r="L546" t="s">
+      <c r="N546" t="s">
         <v>368</v>
       </c>
-      <c r="M546" t="s">
+      <c r="O546" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="547" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B547" t="s">
+    <row r="547" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D547" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="H547" t="s">
+      <c r="J547" t="s">
         <v>367</v>
       </c>
-      <c r="L547" t="s">
+      <c r="N547" t="s">
         <v>368</v>
       </c>
-      <c r="M547" t="s">
+      <c r="O547" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="548" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B548" t="s">
+    <row r="548" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D548" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="H548" t="s">
+      <c r="J548" t="s">
         <v>372</v>
       </c>
-      <c r="I548" t="s">
+      <c r="K548" t="s">
         <v>373</v>
       </c>
-      <c r="L548" t="s">
+      <c r="N548" t="s">
         <v>374</v>
       </c>
-      <c r="M548" t="s">
+      <c r="O548" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="549" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B549" t="s">
+    <row r="549" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D549" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="H549" t="s">
+      <c r="J549" t="s">
         <v>377</v>
       </c>
-      <c r="I549" t="s">
+      <c r="K549" t="s">
         <v>373</v>
       </c>
-      <c r="L549" t="s">
+      <c r="N549" t="s">
         <v>374</v>
       </c>
-      <c r="M549" t="s">
+      <c r="O549" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="550" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B550" t="s">
+    <row r="550" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D550" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="H550" t="s">
+      <c r="J550" t="s">
         <v>379</v>
       </c>
-      <c r="I550" t="s">
+      <c r="K550" t="s">
         <v>373</v>
       </c>
-      <c r="L550" t="s">
+      <c r="N550" t="s">
         <v>374</v>
       </c>
-      <c r="M550" t="s">
+      <c r="O550" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="551" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B551" t="s">
+    <row r="551" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D551" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="H551" t="s">
+      <c r="J551" t="s">
         <v>381</v>
       </c>
-      <c r="I551" t="s">
+      <c r="K551" t="s">
         <v>382</v>
       </c>
-      <c r="L551" t="s">
+      <c r="N551" t="s">
         <v>374</v>
       </c>
-      <c r="M551" t="s">
+      <c r="O551" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="552" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B552" t="s">
+    <row r="552" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D552" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="H552" t="s">
+      <c r="J552" t="s">
         <v>385</v>
       </c>
-      <c r="I552" t="s">
+      <c r="K552" t="s">
         <v>382</v>
       </c>
-      <c r="L552" t="s">
+      <c r="N552" t="s">
         <v>374</v>
       </c>
-      <c r="M552" t="s">
+      <c r="O552" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="553" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B553" t="s">
+    <row r="553" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D553" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="H553" t="s">
+      <c r="J553" t="s">
         <v>387</v>
       </c>
-      <c r="I553" t="s">
+      <c r="K553" t="s">
         <v>388</v>
       </c>
-      <c r="L553" t="s">
+      <c r="N553" t="s">
         <v>374</v>
       </c>
-      <c r="M553" t="s">
+      <c r="O553" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="554" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B554" t="s">
+    <row r="554" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D554" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="H554" t="s">
+      <c r="J554" t="s">
         <v>391</v>
       </c>
-      <c r="I554" t="s">
+      <c r="K554" t="s">
         <v>388</v>
       </c>
-      <c r="L554" t="s">
+      <c r="N554" t="s">
         <v>374</v>
       </c>
-      <c r="M554" t="s">
+      <c r="O554" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="555" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B555" t="s">
+    <row r="555" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D555" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="H555" t="s">
+      <c r="J555" t="s">
         <v>393</v>
       </c>
-      <c r="I555" t="s">
+      <c r="K555" t="s">
         <v>388</v>
       </c>
-      <c r="L555" t="s">
+      <c r="N555" t="s">
         <v>374</v>
       </c>
-      <c r="M555" t="s">
+      <c r="O555" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="556" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B556" t="s">
+    <row r="556" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D556" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="H556" t="s">
+      <c r="J556" t="s">
         <v>396</v>
       </c>
-      <c r="I556" t="s">
+      <c r="K556" t="s">
         <v>397</v>
       </c>
-      <c r="L556" t="s">
+      <c r="N556" t="s">
         <v>398</v>
       </c>
-      <c r="M556" t="s">
+      <c r="O556" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="557" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B557" t="s">
+    <row r="557" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D557" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="H557" t="s">
+      <c r="J557" t="s">
         <v>401</v>
       </c>
-      <c r="I557" t="s">
+      <c r="K557" t="s">
         <v>388</v>
       </c>
-      <c r="L557" t="s">
+      <c r="N557" t="s">
         <v>402</v>
       </c>
-      <c r="M557" t="s">
+      <c r="O557" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="558" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B558" t="s">
+    <row r="558" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D558" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="H558" t="s">
+      <c r="J558" t="s">
         <v>405</v>
       </c>
-      <c r="I558" t="s">
+      <c r="K558" t="s">
         <v>388</v>
       </c>
-      <c r="L558" t="s">
+      <c r="N558" t="s">
         <v>402</v>
       </c>
-      <c r="M558" t="s">
+      <c r="O558" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="559" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B559" t="s">
+    <row r="559" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D559" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="H559" t="s">
+      <c r="J559" t="s">
         <v>407</v>
       </c>
-      <c r="I559" t="s">
+      <c r="K559" t="s">
         <v>388</v>
       </c>
-      <c r="L559" t="s">
+      <c r="N559" t="s">
         <v>402</v>
       </c>
-      <c r="M559" t="s">
+      <c r="O559" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="560" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B560" t="s">
+    <row r="560" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D560" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="H560" t="s">
+      <c r="J560" t="s">
         <v>409</v>
       </c>
-      <c r="I560" t="s">
+      <c r="K560" t="s">
         <v>388</v>
       </c>
-      <c r="L560" t="s">
+      <c r="N560" t="s">
         <v>402</v>
       </c>
-      <c r="M560" t="s">
+      <c r="O560" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="561" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B561" t="s">
+    <row r="561" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D561" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="H561" t="s">
+      <c r="J561" t="s">
         <v>411</v>
       </c>
-      <c r="I561" t="s">
+      <c r="K561" t="s">
         <v>388</v>
       </c>
-      <c r="L561" t="s">
+      <c r="N561" t="s">
         <v>402</v>
       </c>
-      <c r="M561" t="s">
+      <c r="O561" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="562" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B562" t="s">
+    <row r="562" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D562" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="H562" t="s">
+      <c r="J562" t="s">
         <v>413</v>
       </c>
-      <c r="I562" t="s">
+      <c r="K562" t="s">
         <v>388</v>
       </c>
-      <c r="L562" t="s">
+      <c r="N562" t="s">
         <v>402</v>
       </c>
-      <c r="M562" t="s">
+      <c r="O562" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="563" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B563" t="s">
+    <row r="563" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D563" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="H563" t="s">
+      <c r="J563" t="s">
         <v>415</v>
       </c>
-      <c r="I563" t="s">
+      <c r="K563" t="s">
         <v>388</v>
       </c>
-      <c r="L563" t="s">
+      <c r="N563" t="s">
         <v>402</v>
       </c>
-      <c r="M563" t="s">
+      <c r="O563" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="564" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B564" t="s">
+    <row r="564" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D564" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="H564" t="s">
+      <c r="J564" t="s">
         <v>417</v>
       </c>
-      <c r="I564" t="s">
+      <c r="K564" t="s">
         <v>388</v>
       </c>
-      <c r="L564" t="s">
+      <c r="N564" t="s">
         <v>402</v>
       </c>
-      <c r="M564" t="s">
+      <c r="O564" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="565" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B565" t="s">
+    <row r="565" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D565" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H565" t="s">
+      <c r="J565" t="s">
         <v>419</v>
       </c>
-      <c r="I565" t="s">
+      <c r="K565" t="s">
         <v>388</v>
       </c>
-      <c r="L565" t="s">
+      <c r="N565" t="s">
         <v>402</v>
       </c>
-      <c r="M565" t="s">
+      <c r="O565" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="566" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B566" t="s">
+    <row r="566" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D566" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="H566" t="s">
+      <c r="J566" t="s">
         <v>421</v>
       </c>
-      <c r="I566" t="s">
+      <c r="K566" t="s">
         <v>388</v>
       </c>
-      <c r="L566" t="s">
+      <c r="N566" t="s">
         <v>402</v>
       </c>
-      <c r="M566" t="s">
+      <c r="O566" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="567" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B567" t="s">
+    <row r="567" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D567" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="H567" t="s">
+      <c r="J567" t="s">
         <v>423</v>
       </c>
-      <c r="I567" t="s">
+      <c r="K567" t="s">
         <v>388</v>
       </c>
-      <c r="L567" t="s">
+      <c r="N567" t="s">
         <v>402</v>
       </c>
-      <c r="M567" t="s">
+      <c r="O567" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="568" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B568" t="s">
+    <row r="568" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D568" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="H568" t="s">
+      <c r="J568" t="s">
         <v>425</v>
       </c>
-      <c r="I568" t="s">
+      <c r="K568" t="s">
         <v>388</v>
       </c>
-      <c r="L568" t="s">
+      <c r="N568" t="s">
         <v>402</v>
       </c>
-      <c r="M568" t="s">
+      <c r="O568" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="569" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B569" t="s">
+    <row r="569" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D569" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="H569" t="s">
+      <c r="J569" t="s">
         <v>427</v>
       </c>
-      <c r="I569" t="s">
+      <c r="K569" t="s">
         <v>428</v>
       </c>
-      <c r="L569" t="s">
+      <c r="N569" t="s">
         <v>429</v>
       </c>
-      <c r="M569" t="s">
+      <c r="O569" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="570" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B570" t="s">
+    <row r="570" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D570" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="H570" t="s">
+      <c r="J570" t="s">
         <v>432</v>
       </c>
-      <c r="I570" t="s">
+      <c r="K570" t="s">
         <v>428</v>
       </c>
-      <c r="L570" t="s">
+      <c r="N570" t="s">
         <v>429</v>
       </c>
-      <c r="M570" t="s">
+      <c r="O570" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="571" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B571" t="s">
+    <row r="571" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D571" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="H571" t="s">
+      <c r="J571" t="s">
         <v>434</v>
       </c>
-      <c r="I571" t="s">
+      <c r="K571" t="s">
         <v>435</v>
       </c>
-      <c r="L571" t="s">
+      <c r="N571" t="s">
         <v>429</v>
       </c>
-      <c r="M571" t="s">
+      <c r="O571" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="572" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B572" t="s">
+    <row r="572" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D572" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="H572" t="s">
+      <c r="J572" t="s">
         <v>437</v>
       </c>
-      <c r="I572" t="s">
+      <c r="K572" t="s">
         <v>435</v>
       </c>
-      <c r="L572" t="s">
+      <c r="N572" t="s">
         <v>429</v>
       </c>
-      <c r="M572" t="s">
+      <c r="O572" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="573" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B573" t="s">
+    <row r="573" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D573" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="H573" t="s">
+      <c r="J573" t="s">
         <v>439</v>
       </c>
-      <c r="I573" t="s">
+      <c r="K573" t="s">
         <v>435</v>
       </c>
-      <c r="L573" t="s">
+      <c r="N573" t="s">
         <v>429</v>
       </c>
-      <c r="M573" t="s">
+      <c r="O573" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="574" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B574" t="s">
+    <row r="574" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D574" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="H574" t="s">
+      <c r="J574" t="s">
         <v>439</v>
       </c>
-      <c r="I574" t="s">
+      <c r="K574" t="s">
         <v>435</v>
       </c>
-      <c r="L574" t="s">
+      <c r="N574" t="s">
         <v>429</v>
       </c>
-      <c r="M574" t="s">
+      <c r="O574" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="575" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B575" t="s">
+    <row r="575" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D575" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="H575" t="s">
+      <c r="J575" t="s">
         <v>439</v>
       </c>
-      <c r="I575" t="s">
+      <c r="K575" t="s">
         <v>435</v>
       </c>
-      <c r="L575" t="s">
+      <c r="N575" t="s">
         <v>429</v>
       </c>
-      <c r="M575" t="s">
+      <c r="O575" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="576" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B576" t="s">
+    <row r="576" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D576" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="H576" t="s">
+      <c r="J576" t="s">
         <v>443</v>
       </c>
-      <c r="I576" t="s">
+      <c r="K576" t="s">
         <v>382</v>
       </c>
-      <c r="L576" t="s">
+      <c r="N576" t="s">
         <v>444</v>
       </c>
-      <c r="M576" t="s">
+      <c r="O576" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="577" spans="2:13" ht="18.75" customHeight="1">
-      <c r="B577" t="s">
+    <row r="577" spans="4:15" ht="18.75" customHeight="1">
+      <c r="D577" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="H577" t="s">
+      <c r="J577" t="s">
         <v>447</v>
       </c>
-      <c r="I577" t="s">
+      <c r="K577" t="s">
         <v>382</v>
       </c>
-      <c r="L577" t="s">
+      <c r="N577" t="s">
         <v>444</v>
       </c>
-      <c r="M577" t="s">
+      <c r="O577" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="578" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="579" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="580" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="581" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="582" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="583" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="584" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="585" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="586" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="587" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="588" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="589" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="590" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="591" spans="2:13" ht="18.75" customHeight="1"/>
-    <row r="592" spans="2:13" ht="18.75" customHeight="1"/>
+    <row r="578" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="579" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="580" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="581" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="582" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="583" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="584" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="585" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="586" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="587" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="588" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="589" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="590" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="591" spans="4:15" ht="18.75" customHeight="1"/>
+    <row r="592" spans="4:15" ht="18.75" customHeight="1"/>
     <row r="593" ht="18.75" customHeight="1"/>
     <row r="594" ht="18.75" customHeight="1"/>
     <row r="595" ht="18.75" customHeight="1"/>
@@ -8374,35 +8582,40 @@
     <row r="1001" ht="18.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="www.smopfrance.com      "/>
-    <hyperlink ref="C6" r:id="rId2"/>
-    <hyperlink ref="C8" r:id="rId3"/>
-    <hyperlink ref="C13" r:id="rId4" display="mailto:contact@quintessence-biotech.com"/>
-    <hyperlink ref="C14" r:id="rId5"/>
-    <hyperlink ref="C15" r:id="rId6" display="mailto:contact@ocarelab.com"/>
-    <hyperlink ref="C16" r:id="rId7"/>
-    <hyperlink ref="C20" r:id="rId8"/>
-    <hyperlink ref="C21" r:id="rId9"/>
-    <hyperlink ref="C23" r:id="rId10"/>
-    <hyperlink ref="C25" r:id="rId11"/>
-    <hyperlink ref="F26" r:id="rId12" display="tel: (0)3 80 39 60 87"/>
-    <hyperlink ref="C28" r:id="rId13"/>
-    <hyperlink ref="C29" r:id="rId14"/>
-    <hyperlink ref="C30" r:id="rId15"/>
-    <hyperlink ref="C32" r:id="rId16"/>
-    <hyperlink ref="C36" r:id="rId17"/>
-    <hyperlink ref="C37" r:id="rId18"/>
-    <hyperlink ref="E39" r:id="rId19"/>
-    <hyperlink ref="C40" r:id="rId20"/>
-    <hyperlink ref="E40" r:id="rId21"/>
-    <hyperlink ref="C42" r:id="rId22"/>
-    <hyperlink ref="E42" r:id="rId23"/>
-    <hyperlink ref="E43" r:id="rId24"/>
-    <hyperlink ref="C44" r:id="rId25"/>
-    <hyperlink ref="E45" r:id="rId26"/>
+    <hyperlink ref="E5" r:id="rId1" display="www.smopfrance.com      "/>
+    <hyperlink ref="E6" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId3"/>
+    <hyperlink ref="E13" r:id="rId4" display="mailto:contact@quintessence-biotech.com"/>
+    <hyperlink ref="E14" r:id="rId5"/>
+    <hyperlink ref="E15" r:id="rId6"/>
+    <hyperlink ref="E16" r:id="rId7"/>
+    <hyperlink ref="E20" r:id="rId8"/>
+    <hyperlink ref="E21" r:id="rId9"/>
+    <hyperlink ref="E23" r:id="rId10"/>
+    <hyperlink ref="E25" r:id="rId11"/>
+    <hyperlink ref="H26" r:id="rId12" display="tel: (0)3 80 39 60 87"/>
+    <hyperlink ref="E28" r:id="rId13"/>
+    <hyperlink ref="E29" r:id="rId14"/>
+    <hyperlink ref="E30" r:id="rId15"/>
+    <hyperlink ref="E32" r:id="rId16"/>
+    <hyperlink ref="E36" r:id="rId17"/>
+    <hyperlink ref="E37" r:id="rId18"/>
+    <hyperlink ref="G39" r:id="rId19"/>
+    <hyperlink ref="E40" r:id="rId20"/>
+    <hyperlink ref="G40" r:id="rId21"/>
+    <hyperlink ref="E42" r:id="rId22"/>
+    <hyperlink ref="G42" r:id="rId23"/>
+    <hyperlink ref="G43" r:id="rId24"/>
+    <hyperlink ref="E44" r:id="rId25"/>
+    <hyperlink ref="G45" r:id="rId26"/>
+    <hyperlink ref="F6" r:id="rId27"/>
+    <hyperlink ref="E53" r:id="rId28" display="mailto:kader.zaidat@krystalix.com"/>
+    <hyperlink ref="E54" r:id="rId29"/>
+    <hyperlink ref="E55" r:id="rId30" display="mailto:contact@react-therapeutics.com"/>
+    <hyperlink ref="E57" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId27"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId32"/>
 </worksheet>
 </file>
 
